--- a/research/traditional_assets/database/data/israel/israel_shoe.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_shoe.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1021903561584986</v>
+        <v>0.1019899683393341</v>
       </c>
       <c r="C2">
-        <v>136.2435621832523</v>
+        <v>135.3226315214465</v>
       </c>
       <c r="D2">
-        <v>134.0535621832523</v>
+        <v>134.5316315214465</v>
       </c>
       <c r="E2">
-        <v>-101</v>
+        <v>-99.601</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.399</v>
       </c>
       <c r="G2">
         <v>2.19</v>
@@ -1439,28 +1439,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07036969999999999</v>
       </c>
       <c r="N2">
-        <v>8.963333333333335</v>
+        <v>8.892963633333334</v>
       </c>
       <c r="O2">
-        <v>2.061566666666667</v>
+        <v>2.045381635666667</v>
       </c>
       <c r="P2">
-        <v>6.901766666666667</v>
+        <v>6.847581997666667</v>
       </c>
       <c r="Q2">
-        <v>10.42176666666667</v>
+        <v>10.36758199766667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1021903561584986</v>
+        <v>0.1026289478175092</v>
       </c>
       <c r="T2">
-        <v>0.8723408754896529</v>
+        <v>0.8791257489656836</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>127.3748976240248</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1019899683393341</v>
+        <v>0.1017895805201696</v>
       </c>
       <c r="C3">
-        <v>135.3226315214465</v>
+        <v>134.4051228989273</v>
       </c>
       <c r="D3">
-        <v>134.5316315214465</v>
+        <v>135.0131228989273</v>
       </c>
       <c r="E3">
-        <v>-99.601</v>
+        <v>-98.202</v>
       </c>
       <c r="F3">
-        <v>1.399</v>
+        <v>2.798</v>
       </c>
       <c r="G3">
         <v>2.19</v>
@@ -1521,28 +1521,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M3">
-        <v>0.07036969999999999</v>
+        <v>0.1407394</v>
       </c>
       <c r="N3">
-        <v>8.892963633333334</v>
+        <v>8.822593933333335</v>
       </c>
       <c r="O3">
-        <v>2.045381635666667</v>
+        <v>2.029196604666667</v>
       </c>
       <c r="P3">
-        <v>6.847581997666667</v>
+        <v>6.793397328666668</v>
       </c>
       <c r="Q3">
-        <v>10.36758199766667</v>
+        <v>10.31339732866667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1026289478175092</v>
+        <v>0.1030764903267036</v>
       </c>
       <c r="T3">
-        <v>0.8791257489656836</v>
+        <v>0.8860490892473475</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>127.3748976240248</v>
+        <v>63.68744881201238</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1017895805201696</v>
+        <v>0.101589192701005</v>
       </c>
       <c r="C4">
-        <v>134.4051228989273</v>
+        <v>133.4910731903092</v>
       </c>
       <c r="D4">
-        <v>135.0131228989273</v>
+        <v>135.4980731903092</v>
       </c>
       <c r="E4">
-        <v>-98.202</v>
+        <v>-96.803</v>
       </c>
       <c r="F4">
-        <v>2.798</v>
+        <v>4.197</v>
       </c>
       <c r="G4">
         <v>2.19</v>
@@ -1603,28 +1603,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M4">
-        <v>0.1407394</v>
+        <v>0.2111091</v>
       </c>
       <c r="N4">
-        <v>8.822593933333335</v>
+        <v>8.752224233333335</v>
       </c>
       <c r="O4">
-        <v>2.029196604666667</v>
+        <v>2.013011573666667</v>
       </c>
       <c r="P4">
-        <v>6.793397328666668</v>
+        <v>6.739212659666668</v>
       </c>
       <c r="Q4">
-        <v>10.31339732866667</v>
+        <v>10.25921265966667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1030764903267036</v>
+        <v>0.1035332605165</v>
       </c>
       <c r="T4">
-        <v>0.8860490892473475</v>
+        <v>0.8931151788131694</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>63.68744881201238</v>
+        <v>42.45829920800826</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.101589192701005</v>
+        <v>0.1013888048818404</v>
       </c>
       <c r="C5">
-        <v>133.4910731903092</v>
+        <v>132.5805198019124</v>
       </c>
       <c r="D5">
-        <v>135.4980731903092</v>
+        <v>135.9865198019124</v>
       </c>
       <c r="E5">
-        <v>-96.803</v>
+        <v>-95.404</v>
       </c>
       <c r="F5">
-        <v>4.197</v>
+        <v>5.596</v>
       </c>
       <c r="G5">
         <v>2.19</v>
@@ -1685,28 +1685,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M5">
-        <v>0.2111091</v>
+        <v>0.2814788</v>
       </c>
       <c r="N5">
-        <v>8.752224233333335</v>
+        <v>8.681854533333334</v>
       </c>
       <c r="O5">
-        <v>2.013011573666667</v>
+        <v>1.996826542666667</v>
       </c>
       <c r="P5">
-        <v>6.739212659666668</v>
+        <v>6.685027990666668</v>
       </c>
       <c r="Q5">
-        <v>10.25921265966667</v>
+        <v>10.20502799066667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1035332605165</v>
+        <v>0.1039995467519171</v>
       </c>
       <c r="T5">
-        <v>0.8931151788131694</v>
+        <v>0.9003284785782791</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.45829920800826</v>
+        <v>31.84372440600619</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1013888048818404</v>
+        <v>0.1011884170626759</v>
       </c>
       <c r="C6">
-        <v>132.5805198019124</v>
+        <v>131.6735006813812</v>
       </c>
       <c r="D6">
-        <v>135.9865198019124</v>
+        <v>136.4785006813812</v>
       </c>
       <c r="E6">
-        <v>-95.404</v>
+        <v>-94.005</v>
       </c>
       <c r="F6">
-        <v>5.596</v>
+        <v>6.995000000000001</v>
       </c>
       <c r="G6">
         <v>2.19</v>
@@ -1767,28 +1767,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M6">
-        <v>0.2814788</v>
+        <v>0.3518485</v>
       </c>
       <c r="N6">
-        <v>8.681854533333334</v>
+        <v>8.611484833333336</v>
       </c>
       <c r="O6">
-        <v>1.996826542666667</v>
+        <v>1.980641511666667</v>
       </c>
       <c r="P6">
-        <v>6.685027990666668</v>
+        <v>6.630843321666668</v>
       </c>
       <c r="Q6">
-        <v>10.20502799066667</v>
+        <v>10.15084332166667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1039995467519171</v>
+        <v>0.1044756495396588</v>
       </c>
       <c r="T6">
-        <v>0.9003284785782791</v>
+        <v>0.9076936372858125</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.84372440600619</v>
+        <v>25.47497952480495</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1011884170626759</v>
+        <v>0.1009880292435114</v>
       </c>
       <c r="C7">
-        <v>131.6735006813812</v>
+        <v>130.7700543275119</v>
       </c>
       <c r="D7">
-        <v>136.4785006813812</v>
+        <v>136.9740543275119</v>
       </c>
       <c r="E7">
-        <v>-94.005</v>
+        <v>-92.60599999999999</v>
       </c>
       <c r="F7">
-        <v>6.995000000000001</v>
+        <v>8.394</v>
       </c>
       <c r="G7">
         <v>2.19</v>
@@ -1849,28 +1849,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M7">
-        <v>0.3518485</v>
+        <v>0.4222182</v>
       </c>
       <c r="N7">
-        <v>8.611484833333336</v>
+        <v>8.541115133333335</v>
       </c>
       <c r="O7">
-        <v>1.980641511666667</v>
+        <v>1.964456480666667</v>
       </c>
       <c r="P7">
-        <v>6.630843321666668</v>
+        <v>6.576658652666667</v>
       </c>
       <c r="Q7">
-        <v>10.15084332166667</v>
+        <v>10.09665865266667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1044756495396588</v>
+        <v>0.1049618821739483</v>
       </c>
       <c r="T7">
-        <v>0.9076936372858125</v>
+        <v>0.9152155014977614</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.47497952480495</v>
+        <v>21.22914960400413</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1009880292435113</v>
+        <v>0.1007876414243468</v>
       </c>
       <c r="C8">
-        <v>130.7700543275119</v>
+        <v>129.870219800295</v>
       </c>
       <c r="D8">
-        <v>136.9740543275119</v>
+        <v>137.4732198002951</v>
       </c>
       <c r="E8">
-        <v>-92.60599999999999</v>
+        <v>-91.20699999999999</v>
       </c>
       <c r="F8">
-        <v>8.394</v>
+        <v>9.792999999999999</v>
       </c>
       <c r="G8">
         <v>2.19</v>
@@ -1931,28 +1931,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M8">
-        <v>0.4222182</v>
+        <v>0.4925878999999999</v>
       </c>
       <c r="N8">
-        <v>8.541115133333335</v>
+        <v>8.470745433333335</v>
       </c>
       <c r="O8">
-        <v>1.964456480666667</v>
+        <v>1.948271449666667</v>
       </c>
       <c r="P8">
-        <v>6.576658652666667</v>
+        <v>6.522473983666668</v>
       </c>
       <c r="Q8">
-        <v>10.09665865266667</v>
+        <v>10.04247398366667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1049618821739483</v>
+        <v>0.1054585714240288</v>
       </c>
       <c r="T8">
-        <v>0.9152155014977612</v>
+        <v>0.9228991262303972</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.22914960400413</v>
+        <v>18.19641394628925</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1007876414243468</v>
+        <v>0.1005872536051823</v>
       </c>
       <c r="C9">
-        <v>129.8702198002951</v>
+        <v>128.9740367311789</v>
       </c>
       <c r="D9">
-        <v>137.4732198002951</v>
+        <v>137.9760367311789</v>
       </c>
       <c r="E9">
-        <v>-91.20699999999999</v>
+        <v>-89.80799999999999</v>
       </c>
       <c r="F9">
-        <v>9.793000000000001</v>
+        <v>11.192</v>
       </c>
       <c r="G9">
         <v>2.19</v>
@@ -2013,28 +2013,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M9">
-        <v>0.4925879</v>
+        <v>0.5629575999999999</v>
       </c>
       <c r="N9">
-        <v>8.470745433333335</v>
+        <v>8.400375733333334</v>
       </c>
       <c r="O9">
-        <v>1.948271449666667</v>
+        <v>1.932086418666667</v>
       </c>
       <c r="P9">
-        <v>6.522473983666668</v>
+        <v>6.468289314666667</v>
       </c>
       <c r="Q9">
-        <v>10.04247398366667</v>
+        <v>9.988289314666668</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1054585714240288</v>
+        <v>0.1059660582665025</v>
       </c>
       <c r="T9">
-        <v>0.9228991262303972</v>
+        <v>0.9307497862833078</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.19641394628925</v>
+        <v>15.92186220300309</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1005872536051823</v>
+        <v>0.1003868657860177</v>
       </c>
       <c r="C10">
-        <v>128.9740367311789</v>
+        <v>128.0815453335578</v>
       </c>
       <c r="D10">
-        <v>137.9760367311789</v>
+        <v>138.4825453335579</v>
       </c>
       <c r="E10">
-        <v>-89.80799999999999</v>
+        <v>-88.40900000000001</v>
       </c>
       <c r="F10">
-        <v>11.192</v>
+        <v>12.591</v>
       </c>
       <c r="G10">
         <v>2.19</v>
@@ -2095,28 +2095,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M10">
-        <v>0.5629575999999999</v>
+        <v>0.6333272999999999</v>
       </c>
       <c r="N10">
-        <v>8.400375733333334</v>
+        <v>8.330006033333335</v>
       </c>
       <c r="O10">
-        <v>1.932086418666667</v>
+        <v>1.915901387666667</v>
       </c>
       <c r="P10">
-        <v>6.468289314666667</v>
+        <v>6.414104645666668</v>
       </c>
       <c r="Q10">
-        <v>9.988289314666668</v>
+        <v>9.934104645666668</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1059660582665025</v>
+        <v>0.1064846986659536</v>
       </c>
       <c r="T10">
-        <v>0.9307497862833078</v>
+        <v>0.9387729883154035</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.92186220300309</v>
+        <v>14.15276640266942</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1003868657860177</v>
+        <v>0.1003019779668532</v>
       </c>
       <c r="C11">
-        <v>128.0815453335578</v>
+        <v>126.8982344095189</v>
       </c>
       <c r="D11">
-        <v>138.4825453335579</v>
+        <v>138.6982344095189</v>
       </c>
       <c r="E11">
-        <v>-88.40900000000001</v>
+        <v>-87.01000000000001</v>
       </c>
       <c r="F11">
-        <v>12.591</v>
+        <v>13.99</v>
       </c>
       <c r="G11">
         <v>2.19</v>
@@ -2177,45 +2177,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M11">
-        <v>0.6333272999999999</v>
+        <v>0.724682</v>
       </c>
       <c r="N11">
-        <v>8.330006033333335</v>
+        <v>8.238651333333335</v>
       </c>
       <c r="O11">
-        <v>1.915901387666667</v>
+        <v>1.894889806666667</v>
       </c>
       <c r="P11">
-        <v>6.414104645666668</v>
+        <v>6.343761526666668</v>
       </c>
       <c r="Q11">
-        <v>9.934104645666668</v>
+        <v>9.863761526666668</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1064846986659536</v>
+        <v>0.1070148644076147</v>
       </c>
       <c r="T11">
-        <v>0.9387729883154035</v>
+        <v>0.9469744837259899</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.23</v>
       </c>
       <c r="W11">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>14.15276640266942</v>
+        <v>12.36864353376148</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1003019779668532</v>
+        <v>0.1001131401476886</v>
       </c>
       <c r="C12">
-        <v>126.8982344095189</v>
+        <v>125.9814652662996</v>
       </c>
       <c r="D12">
-        <v>138.6982344095189</v>
+        <v>139.1804652662996</v>
       </c>
       <c r="E12">
-        <v>-87.00999999999999</v>
+        <v>-85.611</v>
       </c>
       <c r="F12">
-        <v>13.99</v>
+        <v>15.389</v>
       </c>
       <c r="G12">
         <v>2.19</v>
@@ -2259,28 +2259,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M12">
-        <v>0.724682</v>
+        <v>0.7971502</v>
       </c>
       <c r="N12">
-        <v>8.238651333333335</v>
+        <v>8.166183133333334</v>
       </c>
       <c r="O12">
-        <v>1.894889806666667</v>
+        <v>1.878222120666667</v>
       </c>
       <c r="P12">
-        <v>6.343761526666668</v>
+        <v>6.287961012666667</v>
       </c>
       <c r="Q12">
-        <v>9.863761526666668</v>
+        <v>9.807961012666667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1070148644076147</v>
+        <v>0.107556943986167</v>
       </c>
       <c r="T12">
-        <v>0.9469744837259899</v>
+        <v>0.9553602824042301</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.36864353376148</v>
+        <v>11.24422139432861</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1001131401476886</v>
+        <v>0.09992430232852408</v>
       </c>
       <c r="C13">
-        <v>125.9814652662996</v>
+        <v>125.068061096647</v>
       </c>
       <c r="D13">
-        <v>139.1804652662996</v>
+        <v>139.666061096647</v>
       </c>
       <c r="E13">
-        <v>-85.611</v>
+        <v>-84.212</v>
       </c>
       <c r="F13">
-        <v>15.389</v>
+        <v>16.788</v>
       </c>
       <c r="G13">
         <v>2.19</v>
@@ -2341,28 +2341,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M13">
-        <v>0.7971502</v>
+        <v>0.8696184</v>
       </c>
       <c r="N13">
-        <v>8.166183133333334</v>
+        <v>8.093714933333334</v>
       </c>
       <c r="O13">
-        <v>1.878222120666667</v>
+        <v>1.861554434666667</v>
       </c>
       <c r="P13">
-        <v>6.287961012666667</v>
+        <v>6.232160498666667</v>
       </c>
       <c r="Q13">
-        <v>9.807961012666667</v>
+        <v>9.752160498666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.107556943986167</v>
+        <v>0.108111343555141</v>
       </c>
       <c r="T13">
-        <v>0.9553602824042301</v>
+        <v>0.9639366674160664</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.24422139432861</v>
+        <v>10.30720294480123</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09992430232852408</v>
+        <v>0.09990563450935952</v>
       </c>
       <c r="C14">
-        <v>125.068061096647</v>
+        <v>123.717249437762</v>
       </c>
       <c r="D14">
-        <v>139.666061096647</v>
+        <v>139.714249437762</v>
       </c>
       <c r="E14">
-        <v>-84.212</v>
+        <v>-82.813</v>
       </c>
       <c r="F14">
-        <v>16.788</v>
+        <v>18.187</v>
       </c>
       <c r="G14">
         <v>2.19</v>
@@ -2423,45 +2423,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M14">
-        <v>0.8696184</v>
+        <v>0.9730045</v>
       </c>
       <c r="N14">
-        <v>8.093714933333334</v>
+        <v>7.990328833333335</v>
       </c>
       <c r="O14">
-        <v>1.861554434666667</v>
+        <v>1.837775631666667</v>
       </c>
       <c r="P14">
-        <v>6.232160498666667</v>
+        <v>6.152553201666668</v>
       </c>
       <c r="Q14">
-        <v>9.752160498666667</v>
+        <v>9.672553201666668</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.108111343555141</v>
+        <v>0.1086784879417926</v>
       </c>
       <c r="T14">
-        <v>0.9639366674160664</v>
+        <v>0.972710210704037</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.23</v>
       </c>
       <c r="W14">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.30720294480123</v>
+        <v>9.212016319897117</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09990563450935952</v>
+        <v>0.09972988669019499</v>
       </c>
       <c r="C15">
-        <v>123.717249437762</v>
+        <v>122.7735530950078</v>
       </c>
       <c r="D15">
-        <v>139.714249437762</v>
+        <v>140.1695530950078</v>
       </c>
       <c r="E15">
-        <v>-82.813</v>
+        <v>-81.414</v>
       </c>
       <c r="F15">
-        <v>18.187</v>
+        <v>19.586</v>
       </c>
       <c r="G15">
         <v>2.19</v>
@@ -2505,28 +2505,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M15">
-        <v>0.9730045</v>
+        <v>1.047851</v>
       </c>
       <c r="N15">
-        <v>7.990328833333335</v>
+        <v>7.915482333333335</v>
       </c>
       <c r="O15">
-        <v>1.837775631666667</v>
+        <v>1.820560936666667</v>
       </c>
       <c r="P15">
-        <v>6.152553201666668</v>
+        <v>6.094921396666668</v>
       </c>
       <c r="Q15">
-        <v>9.672553201666668</v>
+        <v>9.614921396666668</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1086784879417926</v>
+        <v>0.1092588217327849</v>
       </c>
       <c r="T15">
-        <v>0.972710210704037</v>
+        <v>0.9816877898824257</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.212016319897117</v>
+        <v>8.55401515419018</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09972988669019499</v>
+        <v>0.09955413887103044</v>
       </c>
       <c r="C16">
-        <v>122.7735530950078</v>
+        <v>121.8328339602044</v>
       </c>
       <c r="D16">
-        <v>140.1695530950078</v>
+        <v>140.6278339602044</v>
       </c>
       <c r="E16">
-        <v>-81.414</v>
+        <v>-80.015</v>
       </c>
       <c r="F16">
-        <v>19.586</v>
+        <v>20.985</v>
       </c>
       <c r="G16">
         <v>2.19</v>
@@ -2587,28 +2587,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M16">
-        <v>1.047851</v>
+        <v>1.1226975</v>
       </c>
       <c r="N16">
-        <v>7.915482333333335</v>
+        <v>7.840635833333335</v>
       </c>
       <c r="O16">
-        <v>1.820560936666667</v>
+        <v>1.803346241666667</v>
       </c>
       <c r="P16">
-        <v>6.094921396666668</v>
+        <v>6.037289591666667</v>
       </c>
       <c r="Q16">
-        <v>9.614921396666668</v>
+        <v>9.557289591666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1092588217327849</v>
+        <v>0.1098528104365064</v>
       </c>
       <c r="T16">
-        <v>0.9816877898824257</v>
+        <v>0.9908766062179528</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.55401515419018</v>
+        <v>7.983747477244168</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09955413887103044</v>
+        <v>0.09947695105186589</v>
       </c>
       <c r="C17">
-        <v>121.8328339602044</v>
+        <v>120.6360577379062</v>
       </c>
       <c r="D17">
-        <v>140.6278339602044</v>
+        <v>140.8300577379062</v>
       </c>
       <c r="E17">
-        <v>-80.015</v>
+        <v>-78.616</v>
       </c>
       <c r="F17">
-        <v>20.985</v>
+        <v>22.384</v>
       </c>
       <c r="G17">
         <v>2.19</v>
@@ -2669,45 +2669,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M17">
-        <v>1.1226975</v>
+        <v>1.2154512</v>
       </c>
       <c r="N17">
-        <v>7.840635833333335</v>
+        <v>7.747882133333334</v>
       </c>
       <c r="O17">
-        <v>1.803346241666667</v>
+        <v>1.782012890666667</v>
       </c>
       <c r="P17">
-        <v>6.037289591666667</v>
+        <v>5.965869242666667</v>
       </c>
       <c r="Q17">
-        <v>9.557289591666667</v>
+        <v>9.485869242666666</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1098528104365064</v>
+        <v>0.1104609417284118</v>
       </c>
       <c r="T17">
-        <v>0.9908766062179528</v>
+        <v>1.000284203894802</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.23</v>
       </c>
       <c r="W17">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.983747477244169</v>
+        <v>7.374490504705853</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09947695105186589</v>
+        <v>0.09930736323270135</v>
       </c>
       <c r="C18">
-        <v>120.6360577379062</v>
+        <v>119.6834086870405</v>
       </c>
       <c r="D18">
-        <v>140.8300577379062</v>
+        <v>141.2764086870405</v>
       </c>
       <c r="E18">
-        <v>-78.616</v>
+        <v>-77.217</v>
       </c>
       <c r="F18">
-        <v>22.384</v>
+        <v>23.783</v>
       </c>
       <c r="G18">
         <v>2.19</v>
@@ -2751,28 +2751,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M18">
-        <v>1.2154512</v>
+        <v>1.2914169</v>
       </c>
       <c r="N18">
-        <v>7.747882133333334</v>
+        <v>7.671916433333335</v>
       </c>
       <c r="O18">
-        <v>1.782012890666667</v>
+        <v>1.764540779666667</v>
       </c>
       <c r="P18">
-        <v>5.965869242666667</v>
+        <v>5.907375653666668</v>
       </c>
       <c r="Q18">
-        <v>9.485869242666666</v>
+        <v>9.427375653666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1104609417284118</v>
+        <v>0.1110837267863872</v>
       </c>
       <c r="T18">
-        <v>1.000284203894802</v>
+        <v>1.009918490672298</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.374490504705853</v>
+        <v>6.940696945605508</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09930736323270135</v>
+        <v>0.0991377754135368</v>
       </c>
       <c r="C19">
-        <v>119.6834086870405</v>
+        <v>118.733597987923</v>
       </c>
       <c r="D19">
-        <v>141.2764086870405</v>
+        <v>141.725597987923</v>
       </c>
       <c r="E19">
-        <v>-77.217</v>
+        <v>-75.818</v>
       </c>
       <c r="F19">
-        <v>23.783</v>
+        <v>25.18200000000001</v>
       </c>
       <c r="G19">
         <v>2.19</v>
@@ -2833,28 +2833,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M19">
-        <v>1.2914169</v>
+        <v>1.3673826</v>
       </c>
       <c r="N19">
-        <v>7.671916433333335</v>
+        <v>7.595950733333335</v>
       </c>
       <c r="O19">
-        <v>1.764540779666667</v>
+        <v>1.747068668666667</v>
       </c>
       <c r="P19">
-        <v>5.907375653666668</v>
+        <v>5.848882064666668</v>
       </c>
       <c r="Q19">
-        <v>9.427375653666667</v>
+        <v>9.368882064666668</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1110837267863872</v>
+        <v>0.1117217017238254</v>
       </c>
       <c r="T19">
-        <v>1.009918490672298</v>
+        <v>1.019787760054123</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.940696945605508</v>
+        <v>6.555102670849646</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09913777541353681</v>
+        <v>0.09896818759437224</v>
       </c>
       <c r="C20">
-        <v>118.7335979879229</v>
+        <v>117.7866528005852</v>
       </c>
       <c r="D20">
-        <v>141.725597987923</v>
+        <v>142.1776528005852</v>
       </c>
       <c r="E20">
-        <v>-75.818</v>
+        <v>-74.419</v>
       </c>
       <c r="F20">
-        <v>25.182</v>
+        <v>26.581</v>
       </c>
       <c r="G20">
         <v>2.19</v>
@@ -2915,28 +2915,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M20">
-        <v>1.3673826</v>
+        <v>1.4433483</v>
       </c>
       <c r="N20">
-        <v>7.595950733333335</v>
+        <v>7.519985033333334</v>
       </c>
       <c r="O20">
-        <v>1.747068668666667</v>
+        <v>1.729596557666667</v>
       </c>
       <c r="P20">
-        <v>5.848882064666668</v>
+        <v>5.790388475666667</v>
       </c>
       <c r="Q20">
-        <v>9.368882064666668</v>
+        <v>9.310388475666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1117217017238254</v>
+        <v>0.1123754291288546</v>
       </c>
       <c r="T20">
-        <v>1.019787760054123</v>
+        <v>1.029900715099697</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.555102670849647</v>
+        <v>6.210097267120717</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09896818759437224</v>
+        <v>0.09895259977520771</v>
       </c>
       <c r="C21">
-        <v>117.7866528005852</v>
+        <v>116.4293485887587</v>
       </c>
       <c r="D21">
-        <v>142.1776528005852</v>
+        <v>142.2193485887587</v>
       </c>
       <c r="E21">
-        <v>-74.419</v>
+        <v>-73.02</v>
       </c>
       <c r="F21">
-        <v>26.581</v>
+        <v>27.98</v>
       </c>
       <c r="G21">
         <v>2.19</v>
@@ -2997,45 +2997,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M21">
-        <v>1.4433483</v>
+        <v>1.547294</v>
       </c>
       <c r="N21">
-        <v>7.519985033333334</v>
+        <v>7.416039333333335</v>
       </c>
       <c r="O21">
-        <v>1.729596557666667</v>
+        <v>1.705689046666667</v>
       </c>
       <c r="P21">
-        <v>5.790388475666667</v>
+        <v>5.710350286666667</v>
       </c>
       <c r="Q21">
-        <v>9.310388475666667</v>
+        <v>9.230350286666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1123754291288546</v>
+        <v>0.1130454997190096</v>
       </c>
       <c r="T21">
-        <v>1.029900715099697</v>
+        <v>1.040266494021411</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.23</v>
       </c>
       <c r="W21">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.210097267120717</v>
+        <v>5.792908996824995</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09895259977520771</v>
+        <v>0.09879071195604318</v>
       </c>
       <c r="C22">
-        <v>116.4293485887587</v>
+        <v>115.4648319035918</v>
       </c>
       <c r="D22">
-        <v>142.2193485887587</v>
+        <v>142.6538319035919</v>
       </c>
       <c r="E22">
-        <v>-73.02</v>
+        <v>-71.621</v>
       </c>
       <c r="F22">
-        <v>27.98</v>
+        <v>29.379</v>
       </c>
       <c r="G22">
         <v>2.19</v>
@@ -3079,28 +3079,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M22">
-        <v>1.547294</v>
+        <v>1.6246587</v>
       </c>
       <c r="N22">
-        <v>7.416039333333335</v>
+        <v>7.338674633333334</v>
       </c>
       <c r="O22">
-        <v>1.705689046666667</v>
+        <v>1.687895165666667</v>
       </c>
       <c r="P22">
-        <v>5.710350286666667</v>
+        <v>5.650779467666667</v>
       </c>
       <c r="Q22">
-        <v>9.230350286666667</v>
+        <v>9.170779467666668</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1130454997190096</v>
+        <v>0.1137325341215736</v>
       </c>
       <c r="T22">
-        <v>1.040266494021411</v>
+        <v>1.050894697725953</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.792908996824995</v>
+        <v>5.517056187452376</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09879071195604318</v>
+        <v>0.09862882413687861</v>
       </c>
       <c r="C23">
-        <v>115.4648319035918</v>
+        <v>114.5029780661206</v>
       </c>
       <c r="D23">
-        <v>142.6538319035919</v>
+        <v>143.0909780661206</v>
       </c>
       <c r="E23">
-        <v>-71.621</v>
+        <v>-70.22199999999999</v>
       </c>
       <c r="F23">
-        <v>29.379</v>
+        <v>30.778</v>
       </c>
       <c r="G23">
         <v>2.19</v>
@@ -3161,28 +3161,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M23">
-        <v>1.6246587</v>
+        <v>1.7020234</v>
       </c>
       <c r="N23">
-        <v>7.338674633333334</v>
+        <v>7.261309933333335</v>
       </c>
       <c r="O23">
-        <v>1.687895165666667</v>
+        <v>1.670101284666667</v>
       </c>
       <c r="P23">
-        <v>5.650779467666667</v>
+        <v>5.591208648666668</v>
       </c>
       <c r="Q23">
-        <v>9.170779467666668</v>
+        <v>9.111208648666668</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1137325341215736</v>
+        <v>0.11443718479087</v>
       </c>
       <c r="T23">
-        <v>1.050894697725953</v>
+        <v>1.061795419474201</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.517056187452376</v>
+        <v>5.266280906204542</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09862882413687861</v>
+        <v>0.09846693631771407</v>
       </c>
       <c r="C24">
-        <v>114.5029780661206</v>
+        <v>113.5438116315573</v>
       </c>
       <c r="D24">
-        <v>143.0909780661206</v>
+        <v>143.5308116315573</v>
       </c>
       <c r="E24">
-        <v>-70.22199999999999</v>
+        <v>-68.82300000000001</v>
       </c>
       <c r="F24">
-        <v>30.778</v>
+        <v>32.177</v>
       </c>
       <c r="G24">
         <v>2.19</v>
@@ -3243,28 +3243,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M24">
-        <v>1.7020234</v>
+        <v>1.7793881</v>
       </c>
       <c r="N24">
-        <v>7.261309933333335</v>
+        <v>7.183945233333334</v>
       </c>
       <c r="O24">
-        <v>1.670101284666667</v>
+        <v>1.652307403666667</v>
       </c>
       <c r="P24">
-        <v>5.591208648666668</v>
+        <v>5.531637829666668</v>
       </c>
       <c r="Q24">
-        <v>9.111208648666668</v>
+        <v>9.051637829666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.11443718479087</v>
+        <v>0.1151601380749533</v>
       </c>
       <c r="T24">
-        <v>1.061795419474201</v>
+        <v>1.072979276852273</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.266280906204542</v>
+        <v>5.03731217115217</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09846693631771407</v>
+        <v>0.09830504849854951</v>
       </c>
       <c r="C25">
-        <v>113.5438116315573</v>
+        <v>112.587357457957</v>
       </c>
       <c r="D25">
-        <v>143.5308116315573</v>
+        <v>143.973357457957</v>
       </c>
       <c r="E25">
-        <v>-68.82300000000001</v>
+        <v>-67.42400000000001</v>
       </c>
       <c r="F25">
-        <v>32.177</v>
+        <v>33.576</v>
       </c>
       <c r="G25">
         <v>2.19</v>
@@ -3325,28 +3325,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M25">
-        <v>1.7793881</v>
+        <v>1.8567528</v>
       </c>
       <c r="N25">
-        <v>7.183945233333334</v>
+        <v>7.106580533333334</v>
       </c>
       <c r="O25">
-        <v>1.652307403666667</v>
+        <v>1.634513522666667</v>
       </c>
       <c r="P25">
-        <v>5.531637829666668</v>
+        <v>5.472067010666667</v>
       </c>
       <c r="Q25">
-        <v>9.051637829666667</v>
+        <v>8.992067010666666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1151601380749533</v>
+        <v>0.1159021164454599</v>
       </c>
       <c r="T25">
-        <v>1.072979276852273</v>
+        <v>1.084457446266611</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.03731217115217</v>
+        <v>4.82742416402083</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09830504849854951</v>
+        <v>0.09814316067938496</v>
       </c>
       <c r="C26">
-        <v>112.587357457957</v>
+        <v>111.6336407109007</v>
       </c>
       <c r="D26">
-        <v>143.973357457957</v>
+        <v>144.4186407109007</v>
       </c>
       <c r="E26">
-        <v>-67.42400000000001</v>
+        <v>-66.02500000000001</v>
       </c>
       <c r="F26">
-        <v>33.576</v>
+        <v>34.975</v>
       </c>
       <c r="G26">
         <v>2.19</v>
@@ -3407,28 +3407,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M26">
-        <v>1.8567528</v>
+        <v>1.9341175</v>
       </c>
       <c r="N26">
-        <v>7.106580533333334</v>
+        <v>7.029215833333335</v>
       </c>
       <c r="O26">
-        <v>1.634513522666667</v>
+        <v>1.616719641666667</v>
       </c>
       <c r="P26">
-        <v>5.472067010666667</v>
+        <v>5.412496191666667</v>
       </c>
       <c r="Q26">
-        <v>8.992067010666666</v>
+        <v>8.932496191666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1159021164454599</v>
+        <v>0.1166638809058466</v>
       </c>
       <c r="T26">
-        <v>1.084457446266611</v>
+        <v>1.096241700198664</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.82742416402083</v>
+        <v>4.634327197459996</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09814316067938496</v>
+        <v>0.09848177286022045</v>
       </c>
       <c r="C27">
-        <v>111.6336407109007</v>
+        <v>109.3063896625891</v>
       </c>
       <c r="D27">
-        <v>144.4186407109007</v>
+        <v>143.4903896625891</v>
       </c>
       <c r="E27">
-        <v>-66.02500000000001</v>
+        <v>-64.626</v>
       </c>
       <c r="F27">
-        <v>34.975</v>
+        <v>36.374</v>
       </c>
       <c r="G27">
         <v>2.19</v>
@@ -3489,45 +3489,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M27">
-        <v>1.9341175</v>
+        <v>2.1024172</v>
       </c>
       <c r="N27">
-        <v>7.029215833333335</v>
+        <v>6.860916133333335</v>
       </c>
       <c r="O27">
-        <v>1.616719641666667</v>
+        <v>1.578010710666667</v>
       </c>
       <c r="P27">
-        <v>5.412496191666667</v>
+        <v>5.282905422666667</v>
       </c>
       <c r="Q27">
-        <v>8.932496191666667</v>
+        <v>8.802905422666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1166638809058466</v>
+        <v>0.1174462335948925</v>
       </c>
       <c r="T27">
-        <v>1.096241700198664</v>
+        <v>1.108344447480232</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.23</v>
       </c>
       <c r="W27">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.634327197459996</v>
+        <v>4.263346653239583</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09848177286022045</v>
+        <v>0.09833913504105588</v>
       </c>
       <c r="C28">
-        <v>109.3063896625891</v>
+        <v>108.2969498682634</v>
       </c>
       <c r="D28">
-        <v>143.4903896625891</v>
+        <v>143.8799498682634</v>
       </c>
       <c r="E28">
-        <v>-64.626</v>
+        <v>-63.227</v>
       </c>
       <c r="F28">
-        <v>36.374</v>
+        <v>37.773</v>
       </c>
       <c r="G28">
         <v>2.19</v>
@@ -3571,28 +3571,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M28">
-        <v>2.1024172</v>
+        <v>2.1832794</v>
       </c>
       <c r="N28">
-        <v>6.860916133333335</v>
+        <v>6.780053933333335</v>
       </c>
       <c r="O28">
-        <v>1.578010710666667</v>
+        <v>1.559412404666667</v>
       </c>
       <c r="P28">
-        <v>5.282905422666667</v>
+        <v>5.220641528666667</v>
       </c>
       <c r="Q28">
-        <v>8.802905422666667</v>
+        <v>8.740641528666668</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1174462335948925</v>
+        <v>0.1182500206041861</v>
       </c>
       <c r="T28">
-        <v>1.108344447480232</v>
+        <v>1.120778776879103</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.263346653239583</v>
+        <v>4.105444925341819</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09833913504105588</v>
+        <v>0.09895109722189133</v>
       </c>
       <c r="C29">
-        <v>108.2969498682634</v>
+        <v>105.2413690542814</v>
       </c>
       <c r="D29">
-        <v>143.8799498682634</v>
+        <v>142.2233690542814</v>
       </c>
       <c r="E29">
-        <v>-63.227</v>
+        <v>-61.828</v>
       </c>
       <c r="F29">
-        <v>37.773</v>
+        <v>39.172</v>
       </c>
       <c r="G29">
         <v>2.19</v>
@@ -3653,45 +3653,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M29">
-        <v>2.1832794</v>
+        <v>2.4012436</v>
       </c>
       <c r="N29">
-        <v>6.780053933333335</v>
+        <v>6.562089733333334</v>
       </c>
       <c r="O29">
-        <v>1.559412404666667</v>
+        <v>1.509280638666667</v>
       </c>
       <c r="P29">
-        <v>5.220641528666667</v>
+        <v>5.052809094666667</v>
       </c>
       <c r="Q29">
-        <v>8.740641528666668</v>
+        <v>8.572809094666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1182500206041861</v>
+        <v>0.1190761350304046</v>
       </c>
       <c r="T29">
-        <v>1.120778776879103</v>
+        <v>1.133558504316832</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0.23</v>
       </c>
       <c r="W29">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.105444925341819</v>
+        <v>3.732788015898651</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09895109722189133</v>
+        <v>0.0988354094027268</v>
       </c>
       <c r="C30">
-        <v>105.2413690542814</v>
+        <v>104.1526053961032</v>
       </c>
       <c r="D30">
-        <v>142.2233690542814</v>
+        <v>142.5336053961032</v>
       </c>
       <c r="E30">
-        <v>-61.828</v>
+        <v>-60.42899999999999</v>
       </c>
       <c r="F30">
-        <v>39.172</v>
+        <v>40.57100000000001</v>
       </c>
       <c r="G30">
         <v>2.19</v>
@@ -3735,28 +3735,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M30">
-        <v>2.4012436</v>
+        <v>2.4870023</v>
       </c>
       <c r="N30">
-        <v>6.562089733333334</v>
+        <v>6.476331033333334</v>
       </c>
       <c r="O30">
-        <v>1.509280638666667</v>
+        <v>1.489556137666667</v>
       </c>
       <c r="P30">
-        <v>5.052809094666667</v>
+        <v>4.986774895666668</v>
       </c>
       <c r="Q30">
-        <v>8.572809094666667</v>
+        <v>8.506774895666668</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1190761350304046</v>
+        <v>0.1199255202855307</v>
       </c>
       <c r="T30">
-        <v>1.133558504316832</v>
+        <v>1.146698224076751</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.732788015898651</v>
+        <v>3.604071187764215</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09883540940272678</v>
+        <v>0.09936652158356224</v>
       </c>
       <c r="C31">
-        <v>104.1526053961032</v>
+        <v>101.3403843810673</v>
       </c>
       <c r="D31">
-        <v>142.5336053961032</v>
+        <v>141.1203843810673</v>
       </c>
       <c r="E31">
-        <v>-60.429</v>
+        <v>-59.03</v>
       </c>
       <c r="F31">
-        <v>40.571</v>
+        <v>41.97</v>
       </c>
       <c r="G31">
         <v>2.19</v>
@@ -3817,45 +3817,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M31">
-        <v>2.4870023</v>
+        <v>2.690277</v>
       </c>
       <c r="N31">
-        <v>6.476331033333334</v>
+        <v>6.273056333333335</v>
       </c>
       <c r="O31">
-        <v>1.489556137666667</v>
+        <v>1.442802956666667</v>
       </c>
       <c r="P31">
-        <v>4.986774895666668</v>
+        <v>4.830253376666668</v>
       </c>
       <c r="Q31">
-        <v>8.506774895666668</v>
+        <v>8.350253376666668</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1199255202855307</v>
+        <v>0.1207991736908032</v>
       </c>
       <c r="T31">
-        <v>1.146698224076751</v>
+        <v>1.160213364401238</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.23</v>
       </c>
       <c r="W31">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.604071187764215</v>
+        <v>3.331751092297683</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09936652158356224</v>
+        <v>0.0992723937643977</v>
       </c>
       <c r="C32">
-        <v>101.3403843810673</v>
+        <v>100.1897995554464</v>
       </c>
       <c r="D32">
-        <v>141.1203843810673</v>
+        <v>141.3687995554464</v>
       </c>
       <c r="E32">
-        <v>-59.03</v>
+        <v>-57.631</v>
       </c>
       <c r="F32">
-        <v>41.97</v>
+        <v>43.369</v>
       </c>
       <c r="G32">
         <v>2.19</v>
@@ -3899,28 +3899,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M32">
-        <v>2.690277</v>
+        <v>2.7799529</v>
       </c>
       <c r="N32">
-        <v>6.273056333333335</v>
+        <v>6.183380433333335</v>
       </c>
       <c r="O32">
-        <v>1.442802956666667</v>
+        <v>1.422177499666667</v>
       </c>
       <c r="P32">
-        <v>4.830253376666668</v>
+        <v>4.761202933666668</v>
       </c>
       <c r="Q32">
-        <v>8.350253376666668</v>
+        <v>8.281202933666668</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1207991736908032</v>
+        <v>0.1216981503831851</v>
       </c>
       <c r="T32">
-        <v>1.160213364401238</v>
+        <v>1.174120247923537</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.331751092297683</v>
+        <v>3.224275250610662</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0992723937643977</v>
+        <v>0.09917826594523313</v>
       </c>
       <c r="C33">
-        <v>100.1897995554464</v>
+        <v>99.04009084590757</v>
       </c>
       <c r="D33">
-        <v>141.3687995554464</v>
+        <v>141.6180908459076</v>
       </c>
       <c r="E33">
-        <v>-57.631</v>
+        <v>-56.232</v>
       </c>
       <c r="F33">
-        <v>43.369</v>
+        <v>44.768</v>
       </c>
       <c r="G33">
         <v>2.19</v>
@@ -3981,28 +3981,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M33">
-        <v>2.7799529</v>
+        <v>2.8696288</v>
       </c>
       <c r="N33">
-        <v>6.183380433333335</v>
+        <v>6.093704533333335</v>
       </c>
       <c r="O33">
-        <v>1.422177499666667</v>
+        <v>1.401552042666667</v>
       </c>
       <c r="P33">
-        <v>4.761202933666668</v>
+        <v>4.692152490666667</v>
       </c>
       <c r="Q33">
-        <v>8.281202933666668</v>
+        <v>8.212152490666668</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1216981503831851</v>
+        <v>0.1226235675665193</v>
       </c>
       <c r="T33">
-        <v>1.174120247923537</v>
+        <v>1.188436157431786</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.224275250610662</v>
+        <v>3.123516649029078</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09917826594523313</v>
+        <v>0.09908413812606859</v>
       </c>
       <c r="C34">
-        <v>99.04009084590757</v>
+        <v>97.89126289549637</v>
       </c>
       <c r="D34">
-        <v>141.6180908459076</v>
+        <v>141.8682628954964</v>
       </c>
       <c r="E34">
-        <v>-56.232</v>
+        <v>-54.833</v>
       </c>
       <c r="F34">
-        <v>44.768</v>
+        <v>46.167</v>
       </c>
       <c r="G34">
         <v>2.19</v>
@@ -4063,28 +4063,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M34">
-        <v>2.8696288</v>
+        <v>2.9593047</v>
       </c>
       <c r="N34">
-        <v>6.093704533333335</v>
+        <v>6.004028633333334</v>
       </c>
       <c r="O34">
-        <v>1.401552042666667</v>
+        <v>1.380926585666667</v>
       </c>
       <c r="P34">
-        <v>4.692152490666667</v>
+        <v>4.623102047666667</v>
       </c>
       <c r="Q34">
-        <v>8.212152490666668</v>
+        <v>8.143102047666668</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1226235675665193</v>
+        <v>0.123576609143386</v>
       </c>
       <c r="T34">
-        <v>1.188436157431786</v>
+        <v>1.203179407522371</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.123516649029078</v>
+        <v>3.02886462936153</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09908413812606859</v>
+        <v>0.101032050306904</v>
       </c>
       <c r="C35">
-        <v>97.89126289549637</v>
+        <v>91.48888323038261</v>
       </c>
       <c r="D35">
-        <v>141.8682628954964</v>
+        <v>136.8648832303826</v>
       </c>
       <c r="E35">
-        <v>-54.833</v>
+        <v>-53.434</v>
       </c>
       <c r="F35">
-        <v>46.167</v>
+        <v>47.566</v>
       </c>
       <c r="G35">
         <v>2.19</v>
@@ -4145,45 +4145,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M35">
-        <v>2.9593047</v>
+        <v>3.4199954</v>
       </c>
       <c r="N35">
-        <v>6.004028633333334</v>
+        <v>5.543337933333334</v>
       </c>
       <c r="O35">
-        <v>1.380926585666667</v>
+        <v>1.274967724666667</v>
       </c>
       <c r="P35">
-        <v>4.623102047666667</v>
+        <v>4.268370208666667</v>
       </c>
       <c r="Q35">
-        <v>8.143102047666668</v>
+        <v>7.788370208666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.123576609143386</v>
+        <v>0.1245585307680364</v>
       </c>
       <c r="T35">
-        <v>1.203179407522371</v>
+        <v>1.218369422767215</v>
       </c>
       <c r="U35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0.23</v>
       </c>
       <c r="W35">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.02886462936153</v>
+        <v>2.620861224940049</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.101032050306904</v>
+        <v>0.1009979824877395</v>
       </c>
       <c r="C36">
-        <v>91.48888323038261</v>
+        <v>90.1743553049354</v>
       </c>
       <c r="D36">
-        <v>136.8648832303826</v>
+        <v>136.9493553049354</v>
       </c>
       <c r="E36">
-        <v>-53.434</v>
+        <v>-52.035</v>
       </c>
       <c r="F36">
-        <v>47.566</v>
+        <v>48.965</v>
       </c>
       <c r="G36">
         <v>2.19</v>
@@ -4227,28 +4227,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M36">
-        <v>3.4199954</v>
+        <v>3.5205835</v>
       </c>
       <c r="N36">
-        <v>5.543337933333334</v>
+        <v>5.442749833333334</v>
       </c>
       <c r="O36">
-        <v>1.274967724666667</v>
+        <v>1.251832461666667</v>
       </c>
       <c r="P36">
-        <v>4.268370208666667</v>
+        <v>4.190917371666667</v>
       </c>
       <c r="Q36">
-        <v>7.788370208666667</v>
+        <v>7.710917371666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1245585307680364</v>
+        <v>0.1255706653657531</v>
       </c>
       <c r="T36">
-        <v>1.218369422767215</v>
+        <v>1.234026823096517</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.620861224940049</v>
+        <v>2.545979475656048</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1009979824877395</v>
+        <v>0.102044994668575</v>
       </c>
       <c r="C37">
-        <v>90.1743553049354</v>
+        <v>86.22601479905137</v>
       </c>
       <c r="D37">
-        <v>136.9493553049354</v>
+        <v>134.4000147990514</v>
       </c>
       <c r="E37">
-        <v>-52.035</v>
+        <v>-50.63599999999999</v>
       </c>
       <c r="F37">
-        <v>48.965</v>
+        <v>50.36400000000001</v>
       </c>
       <c r="G37">
         <v>2.19</v>
@@ -4309,45 +4309,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M37">
-        <v>3.5205835</v>
+        <v>3.817591200000001</v>
       </c>
       <c r="N37">
-        <v>5.442749833333334</v>
+        <v>5.145742133333334</v>
       </c>
       <c r="O37">
-        <v>1.251832461666667</v>
+        <v>1.183520690666667</v>
       </c>
       <c r="P37">
-        <v>4.190917371666667</v>
+        <v>3.962221442666667</v>
       </c>
       <c r="Q37">
-        <v>7.710917371666667</v>
+        <v>7.482221442666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1255706653657531</v>
+        <v>0.1266144291696484</v>
       </c>
       <c r="T37">
-        <v>1.234026823096517</v>
+        <v>1.250173517186109</v>
       </c>
       <c r="U37">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
         <v>0.23</v>
       </c>
       <c r="W37">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.545979475656048</v>
+        <v>2.347902869572136</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.102044994668575</v>
+        <v>0.1020409568494104</v>
       </c>
       <c r="C38">
-        <v>86.22601479905134</v>
+        <v>84.83666404731935</v>
       </c>
       <c r="D38">
-        <v>134.4000147990513</v>
+        <v>134.4096640473194</v>
       </c>
       <c r="E38">
-        <v>-50.636</v>
+        <v>-49.237</v>
       </c>
       <c r="F38">
-        <v>50.364</v>
+        <v>51.763</v>
       </c>
       <c r="G38">
         <v>2.19</v>
@@ -4391,28 +4391,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M38">
-        <v>3.8175912</v>
+        <v>3.9236354</v>
       </c>
       <c r="N38">
-        <v>5.145742133333334</v>
+        <v>5.039697933333334</v>
       </c>
       <c r="O38">
-        <v>1.183520690666667</v>
+        <v>1.159130524666667</v>
       </c>
       <c r="P38">
-        <v>3.962221442666667</v>
+        <v>3.880567408666668</v>
       </c>
       <c r="Q38">
-        <v>7.482221442666667</v>
+        <v>7.400567408666667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1266144291696484</v>
+        <v>0.1276913283323975</v>
       </c>
       <c r="T38">
-        <v>1.250173517186109</v>
+        <v>1.266832804738863</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.347902869572136</v>
+        <v>2.284446035259376</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1020409568494104</v>
+        <v>0.1020369190302459</v>
       </c>
       <c r="C39">
-        <v>84.83666404731935</v>
+        <v>83.44731468122228</v>
       </c>
       <c r="D39">
-        <v>134.4096640473194</v>
+        <v>134.4193146812223</v>
       </c>
       <c r="E39">
-        <v>-49.237</v>
+        <v>-47.83799999999999</v>
       </c>
       <c r="F39">
-        <v>51.763</v>
+        <v>53.16200000000001</v>
       </c>
       <c r="G39">
         <v>2.19</v>
@@ -4473,28 +4473,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M39">
-        <v>3.9236354</v>
+        <v>4.029679600000001</v>
       </c>
       <c r="N39">
-        <v>5.039697933333334</v>
+        <v>4.933653733333334</v>
       </c>
       <c r="O39">
-        <v>1.159130524666667</v>
+        <v>1.134740358666667</v>
       </c>
       <c r="P39">
-        <v>3.880567408666668</v>
+        <v>3.798913374666667</v>
       </c>
       <c r="Q39">
-        <v>7.400567408666667</v>
+        <v>7.318913374666668</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1276913283323975</v>
+        <v>0.1288029661778159</v>
       </c>
       <c r="T39">
-        <v>1.266832804738863</v>
+        <v>1.284029488664286</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.284446035259376</v>
+        <v>2.224329034331497</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1020369190302459</v>
+        <v>0.1020328812110813</v>
       </c>
       <c r="C40">
-        <v>83.44731468122228</v>
+        <v>82.05796670105863</v>
       </c>
       <c r="D40">
-        <v>134.4193146812223</v>
+        <v>134.4289667010586</v>
       </c>
       <c r="E40">
-        <v>-47.83799999999999</v>
+        <v>-46.43899999999999</v>
       </c>
       <c r="F40">
-        <v>53.16200000000001</v>
+        <v>54.56100000000001</v>
       </c>
       <c r="G40">
         <v>2.19</v>
@@ -4555,28 +4555,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M40">
-        <v>4.029679600000001</v>
+        <v>4.135723800000001</v>
       </c>
       <c r="N40">
-        <v>4.933653733333334</v>
+        <v>4.827609533333334</v>
       </c>
       <c r="O40">
-        <v>1.134740358666667</v>
+        <v>1.110350192666667</v>
       </c>
       <c r="P40">
-        <v>3.798913374666667</v>
+        <v>3.717259340666667</v>
       </c>
       <c r="Q40">
-        <v>7.318913374666668</v>
+        <v>7.237259340666666</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1288029661778159</v>
+        <v>0.1299510511657071</v>
       </c>
       <c r="T40">
-        <v>1.284029488664286</v>
+        <v>1.301789998292182</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.224329034331497</v>
+        <v>2.167294956528125</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1020328812110813</v>
+        <v>0.1020288433919168</v>
       </c>
       <c r="C41">
-        <v>82.05796670105863</v>
+        <v>80.66862010712703</v>
       </c>
       <c r="D41">
-        <v>134.4289667010586</v>
+        <v>134.438620107127</v>
       </c>
       <c r="E41">
-        <v>-46.43899999999999</v>
+        <v>-45.03999999999999</v>
       </c>
       <c r="F41">
-        <v>54.56100000000001</v>
+        <v>55.96000000000001</v>
       </c>
       <c r="G41">
         <v>2.19</v>
@@ -4637,28 +4637,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M41">
-        <v>4.135723800000001</v>
+        <v>4.241768000000001</v>
       </c>
       <c r="N41">
-        <v>4.827609533333334</v>
+        <v>4.721565333333333</v>
       </c>
       <c r="O41">
-        <v>1.110350192666667</v>
+        <v>1.085960026666667</v>
       </c>
       <c r="P41">
-        <v>3.717259340666667</v>
+        <v>3.635605306666667</v>
       </c>
       <c r="Q41">
-        <v>7.237259340666666</v>
+        <v>7.155605306666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1299510511657071</v>
+        <v>0.1311374056531946</v>
       </c>
       <c r="T41">
-        <v>1.301789998292182</v>
+        <v>1.320142524907675</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.167294956528125</v>
+        <v>2.113112582614922</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1020288433919168</v>
+        <v>0.1020248055727522</v>
       </c>
       <c r="C42">
-        <v>80.66862010712703</v>
+        <v>79.27927489972603</v>
       </c>
       <c r="D42">
-        <v>134.438620107127</v>
+        <v>134.448274899726</v>
       </c>
       <c r="E42">
-        <v>-45.03999999999999</v>
+        <v>-43.64099999999999</v>
       </c>
       <c r="F42">
-        <v>55.96000000000001</v>
+        <v>57.35900000000001</v>
       </c>
       <c r="G42">
         <v>2.19</v>
@@ -4719,28 +4719,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M42">
-        <v>4.241768000000001</v>
+        <v>4.347812200000001</v>
       </c>
       <c r="N42">
-        <v>4.721565333333333</v>
+        <v>4.615521133333334</v>
       </c>
       <c r="O42">
-        <v>1.085960026666667</v>
+        <v>1.061569860666667</v>
       </c>
       <c r="P42">
-        <v>3.635605306666667</v>
+        <v>3.553951272666667</v>
       </c>
       <c r="Q42">
-        <v>7.155605306666667</v>
+        <v>7.073951272666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1311374056531946</v>
+        <v>0.1323639755470377</v>
       </c>
       <c r="T42">
-        <v>1.320142524907675</v>
+        <v>1.339117171069455</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.113112582614922</v>
+        <v>2.061573251331631</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1020248055727522</v>
+        <v>0.1020207677535877</v>
       </c>
       <c r="C43">
-        <v>79.27927489972603</v>
+        <v>77.88993107915442</v>
       </c>
       <c r="D43">
-        <v>134.448274899726</v>
+        <v>134.4579310791544</v>
       </c>
       <c r="E43">
-        <v>-43.64099999999999</v>
+        <v>-42.24199999999999</v>
       </c>
       <c r="F43">
-        <v>57.35900000000001</v>
+        <v>58.75800000000001</v>
       </c>
       <c r="G43">
         <v>2.19</v>
@@ -4801,28 +4801,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M43">
-        <v>4.347812200000001</v>
+        <v>4.453856400000001</v>
       </c>
       <c r="N43">
-        <v>4.615521133333334</v>
+        <v>4.509476933333334</v>
       </c>
       <c r="O43">
-        <v>1.061569860666667</v>
+        <v>1.037179694666667</v>
       </c>
       <c r="P43">
-        <v>3.553951272666667</v>
+        <v>3.472297238666667</v>
       </c>
       <c r="Q43">
-        <v>7.073951272666667</v>
+        <v>6.992297238666668</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1323639755470377</v>
+        <v>0.1336328409544615</v>
       </c>
       <c r="T43">
-        <v>1.339117171069455</v>
+        <v>1.358746115374746</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.061573251331631</v>
+        <v>2.012488173918973</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1020207677535877</v>
+        <v>0.1067183499344231</v>
       </c>
       <c r="C44">
-        <v>77.88993107915442</v>
+        <v>66.12250872711491</v>
       </c>
       <c r="D44">
-        <v>134.4579310791544</v>
+        <v>124.0895087271149</v>
       </c>
       <c r="E44">
-        <v>-42.242</v>
+        <v>-40.843</v>
       </c>
       <c r="F44">
-        <v>58.758</v>
+        <v>60.157</v>
       </c>
       <c r="G44">
         <v>2.19</v>
@@ -4883,45 +4883,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M44">
-        <v>4.4538564</v>
+        <v>5.41413</v>
       </c>
       <c r="N44">
-        <v>4.509476933333334</v>
+        <v>3.549203333333335</v>
       </c>
       <c r="O44">
-        <v>1.037179694666667</v>
+        <v>0.816316766666667</v>
       </c>
       <c r="P44">
-        <v>3.472297238666668</v>
+        <v>2.732886566666668</v>
       </c>
       <c r="Q44">
-        <v>6.992297238666668</v>
+        <v>6.252886566666668</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1336328409544615</v>
+        <v>0.1349462279551283</v>
       </c>
       <c r="T44">
-        <v>1.358746115374745</v>
+        <v>1.379063794567941</v>
       </c>
       <c r="U44">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V44">
         <v>0.23</v>
       </c>
       <c r="W44">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.012488173918974</v>
+        <v>1.655544535009934</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1067183499344231</v>
+        <v>0.1068236521152586</v>
       </c>
       <c r="C45">
-        <v>66.12250872711491</v>
+        <v>64.50938034517068</v>
       </c>
       <c r="D45">
-        <v>124.0895087271149</v>
+        <v>123.8753803451707</v>
       </c>
       <c r="E45">
-        <v>-40.843</v>
+        <v>-39.444</v>
       </c>
       <c r="F45">
-        <v>60.157</v>
+        <v>61.556</v>
       </c>
       <c r="G45">
         <v>2.19</v>
@@ -4965,28 +4965,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M45">
-        <v>5.41413</v>
+        <v>5.54004</v>
       </c>
       <c r="N45">
-        <v>3.549203333333335</v>
+        <v>3.423293333333334</v>
       </c>
       <c r="O45">
-        <v>0.816316766666667</v>
+        <v>0.7873574666666669</v>
       </c>
       <c r="P45">
-        <v>2.732886566666668</v>
+        <v>2.635935866666667</v>
       </c>
       <c r="Q45">
-        <v>6.252886566666668</v>
+        <v>6.155935866666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1349462279551283</v>
+        <v>0.1363065216343903</v>
       </c>
       <c r="T45">
-        <v>1.379063794567941</v>
+        <v>1.400107105160893</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.655544535009934</v>
+        <v>1.617918522850617</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1068236521152586</v>
+        <v>0.106928954296094</v>
       </c>
       <c r="C46">
-        <v>64.50938034517068</v>
+        <v>62.89698968844555</v>
       </c>
       <c r="D46">
-        <v>123.8753803451707</v>
+        <v>123.6619896884456</v>
       </c>
       <c r="E46">
-        <v>-39.444</v>
+        <v>-38.04499999999999</v>
       </c>
       <c r="F46">
-        <v>61.556</v>
+        <v>62.95500000000001</v>
       </c>
       <c r="G46">
         <v>2.19</v>
@@ -5047,28 +5047,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M46">
-        <v>5.54004</v>
+        <v>5.66595</v>
       </c>
       <c r="N46">
-        <v>3.423293333333334</v>
+        <v>3.297383333333334</v>
       </c>
       <c r="O46">
-        <v>0.7873574666666669</v>
+        <v>0.7583981666666669</v>
       </c>
       <c r="P46">
-        <v>2.635935866666667</v>
+        <v>2.538985166666667</v>
       </c>
       <c r="Q46">
-        <v>6.155935866666667</v>
+        <v>6.058985166666668</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1363065216343903</v>
+        <v>0.1377162805383528</v>
       </c>
       <c r="T46">
-        <v>1.400107105160893</v>
+        <v>1.421915627048134</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.617918522850617</v>
+        <v>1.581964777898381</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.106928954296094</v>
+        <v>0.1070342564769295</v>
       </c>
       <c r="C47">
-        <v>62.89698968844555</v>
+        <v>61.28533295102679</v>
       </c>
       <c r="D47">
-        <v>123.6619896884456</v>
+        <v>123.4493329510268</v>
       </c>
       <c r="E47">
-        <v>-38.04499999999999</v>
+        <v>-36.646</v>
       </c>
       <c r="F47">
-        <v>62.95500000000001</v>
+        <v>64.354</v>
       </c>
       <c r="G47">
         <v>2.19</v>
@@ -5129,28 +5129,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M47">
-        <v>5.66595</v>
+        <v>5.79186</v>
       </c>
       <c r="N47">
-        <v>3.297383333333334</v>
+        <v>3.171473333333335</v>
       </c>
       <c r="O47">
-        <v>0.7583981666666669</v>
+        <v>0.729438866666667</v>
       </c>
       <c r="P47">
-        <v>2.538985166666667</v>
+        <v>2.442034466666668</v>
       </c>
       <c r="Q47">
-        <v>6.058985166666668</v>
+        <v>5.962034466666668</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1377162805383528</v>
+        <v>0.1391782527350546</v>
       </c>
       <c r="T47">
-        <v>1.421915627048134</v>
+        <v>1.444531871968237</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.581964777898381</v>
+        <v>1.547574239248417</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1070342564769295</v>
+        <v>0.1071395586577649</v>
       </c>
       <c r="C48">
-        <v>61.28533295102679</v>
+        <v>59.67440635313663</v>
       </c>
       <c r="D48">
-        <v>123.4493329510268</v>
+        <v>123.2374063531366</v>
       </c>
       <c r="E48">
-        <v>-36.646</v>
+        <v>-35.247</v>
       </c>
       <c r="F48">
-        <v>64.354</v>
+        <v>65.753</v>
       </c>
       <c r="G48">
         <v>2.19</v>
@@ -5211,28 +5211,28 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M48">
-        <v>5.79186</v>
+        <v>5.91777</v>
       </c>
       <c r="N48">
-        <v>3.171473333333335</v>
+        <v>3.045563333333335</v>
       </c>
       <c r="O48">
-        <v>0.729438866666667</v>
+        <v>0.700479566666667</v>
       </c>
       <c r="P48">
-        <v>2.442034466666668</v>
+        <v>2.345083766666668</v>
       </c>
       <c r="Q48">
-        <v>5.962034466666668</v>
+        <v>5.865083766666668</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1391782527350546</v>
+        <v>0.1406953936938961</v>
       </c>
       <c r="T48">
-        <v>1.444531871968237</v>
+        <v>1.46800156009287</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.547574239248417</v>
+        <v>1.514647127775046</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1071395586577649</v>
+        <v>0.1302738065967988</v>
       </c>
       <c r="C49">
-        <v>59.67440635313663</v>
+        <v>24.52524368383681</v>
       </c>
       <c r="D49">
-        <v>123.2374063531366</v>
+        <v>89.48724368383681</v>
       </c>
       <c r="E49">
-        <v>-35.247</v>
+        <v>-33.848</v>
       </c>
       <c r="F49">
-        <v>65.753</v>
+        <v>67.152</v>
       </c>
       <c r="G49">
         <v>2.19</v>
@@ -5293,45 +5293,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M49">
-        <v>5.91777</v>
+        <v>9.857913600000002</v>
       </c>
       <c r="N49">
-        <v>3.045563333333335</v>
+        <v>-0.8945802666666669</v>
       </c>
       <c r="O49">
-        <v>0.700479566666667</v>
+        <v>-0.2057534613333334</v>
       </c>
       <c r="P49">
-        <v>2.345083766666668</v>
+        <v>-0.6888268053333335</v>
       </c>
       <c r="Q49">
-        <v>5.865083766666668</v>
+        <v>2.831173194666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1406953936938961</v>
+        <v>0.1433573240440812</v>
       </c>
       <c r="T49">
-        <v>1.46800156009287</v>
+        <v>1.509180776014936</v>
       </c>
       <c r="U49">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.23</v>
+        <v>0.2091280924461203</v>
       </c>
       <c r="W49">
-        <v>0.0693</v>
+        <v>0.1160999960289096</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.514647127775046</v>
+        <v>0.909252575852697</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1302738065967988</v>
+        <v>0.1312838065967988</v>
       </c>
       <c r="C50">
-        <v>24.52524368383681</v>
+        <v>22.06894266135215</v>
       </c>
       <c r="D50">
-        <v>89.48724368383681</v>
+        <v>88.42994266135216</v>
       </c>
       <c r="E50">
-        <v>-33.848</v>
+        <v>-32.449</v>
       </c>
       <c r="F50">
-        <v>67.152</v>
+        <v>68.551</v>
       </c>
       <c r="G50">
         <v>2.19</v>
@@ -5375,37 +5375,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M50">
-        <v>9.857913600000002</v>
+        <v>10.0632868</v>
       </c>
       <c r="N50">
-        <v>-0.8945802666666669</v>
+        <v>-1.099953466666667</v>
       </c>
       <c r="O50">
-        <v>-0.2057534613333334</v>
+        <v>-0.2529892973333335</v>
       </c>
       <c r="P50">
-        <v>-0.6888268053333335</v>
+        <v>-0.8469641693333338</v>
       </c>
       <c r="Q50">
-        <v>2.831173194666667</v>
+        <v>2.673035830666666</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1433573240440812</v>
+        <v>0.1452702127508279</v>
       </c>
       <c r="T50">
-        <v>1.509180776014936</v>
+        <v>1.538772555936797</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2091280924461203</v>
+        <v>0.2048601721921179</v>
       </c>
       <c r="W50">
-        <v>0.1160999960289096</v>
+        <v>0.1167265267221971</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.909252575852697</v>
+        <v>0.890696400835295</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1312838065967988</v>
+        <v>0.1322938065967988</v>
       </c>
       <c r="C51">
-        <v>22.06894266135215</v>
+        <v>19.6373341359312</v>
       </c>
       <c r="D51">
-        <v>88.42994266135216</v>
+        <v>87.3973341359312</v>
       </c>
       <c r="E51">
-        <v>-32.449</v>
+        <v>-31.05</v>
       </c>
       <c r="F51">
-        <v>68.551</v>
+        <v>69.95</v>
       </c>
       <c r="G51">
         <v>2.19</v>
@@ -5457,37 +5457,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M51">
-        <v>10.0632868</v>
+        <v>10.26866</v>
       </c>
       <c r="N51">
-        <v>-1.099953466666667</v>
+        <v>-1.305326666666666</v>
       </c>
       <c r="O51">
-        <v>-0.2529892973333335</v>
+        <v>-0.3002251333333332</v>
       </c>
       <c r="P51">
-        <v>-0.8469641693333338</v>
+        <v>-1.005101533333333</v>
       </c>
       <c r="Q51">
-        <v>2.673035830666666</v>
+        <v>2.514898466666668</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1452702127508279</v>
+        <v>0.1472596170058445</v>
       </c>
       <c r="T51">
-        <v>1.538772555936797</v>
+        <v>1.569548007055533</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2048601721921179</v>
+        <v>0.2007629687482755</v>
       </c>
       <c r="W51">
-        <v>0.1167265267221971</v>
+        <v>0.1173279961877532</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.890696400835295</v>
+        <v>0.8728824728185892</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1322938065967988</v>
+        <v>0.1333038065967988</v>
       </c>
       <c r="C52">
-        <v>19.6373341359312</v>
+        <v>17.22956307887276</v>
       </c>
       <c r="D52">
-        <v>87.3973341359312</v>
+        <v>86.38856307887276</v>
       </c>
       <c r="E52">
-        <v>-31.05</v>
+        <v>-29.651</v>
       </c>
       <c r="F52">
-        <v>69.95</v>
+        <v>71.349</v>
       </c>
       <c r="G52">
         <v>2.19</v>
@@ -5539,37 +5539,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M52">
-        <v>10.26866</v>
+        <v>10.4740332</v>
       </c>
       <c r="N52">
-        <v>-1.305326666666666</v>
+        <v>-1.510699866666666</v>
       </c>
       <c r="O52">
-        <v>-0.3002251333333332</v>
+        <v>-0.3474609693333333</v>
       </c>
       <c r="P52">
-        <v>-1.005101533333333</v>
+        <v>-1.163238897333333</v>
       </c>
       <c r="Q52">
-        <v>2.514898466666668</v>
+        <v>2.356761102666667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1472596170058445</v>
+        <v>0.1493302214345352</v>
       </c>
       <c r="T52">
-        <v>1.569548007055533</v>
+        <v>1.601579599036258</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2007629687482755</v>
+        <v>0.1968264399492897</v>
       </c>
       <c r="W52">
-        <v>0.1173279961877532</v>
+        <v>0.1179058786154443</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8728824728185892</v>
+        <v>0.8557671302143031</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1333038065967988</v>
+        <v>0.1343138065967988</v>
       </c>
       <c r="C53">
-        <v>17.22956307887276</v>
+        <v>14.84481348720605</v>
       </c>
       <c r="D53">
-        <v>86.38856307887276</v>
+        <v>85.40281348720606</v>
       </c>
       <c r="E53">
-        <v>-29.651</v>
+        <v>-28.252</v>
       </c>
       <c r="F53">
-        <v>71.349</v>
+        <v>72.748</v>
       </c>
       <c r="G53">
         <v>2.19</v>
@@ -5621,37 +5621,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M53">
-        <v>10.4740332</v>
+        <v>10.6794064</v>
       </c>
       <c r="N53">
-        <v>-1.510699866666666</v>
+        <v>-1.716073066666667</v>
       </c>
       <c r="O53">
-        <v>-0.3474609693333333</v>
+        <v>-0.3946968053333333</v>
       </c>
       <c r="P53">
-        <v>-1.163238897333333</v>
+        <v>-1.321376261333333</v>
       </c>
       <c r="Q53">
-        <v>2.356761102666667</v>
+        <v>2.198623738666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1493302214345352</v>
+        <v>0.1514871010477547</v>
       </c>
       <c r="T53">
-        <v>1.601579599036258</v>
+        <v>1.634945840682847</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1968264399492897</v>
+        <v>0.1930413161041111</v>
       </c>
       <c r="W53">
-        <v>0.1179058786154443</v>
+        <v>0.1184615347959165</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8557671302143031</v>
+        <v>0.8393100700178742</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1343138065967988</v>
+        <v>0.1353238065967988</v>
       </c>
       <c r="C54">
-        <v>14.84481348720605</v>
+        <v>12.48230618226576</v>
       </c>
       <c r="D54">
-        <v>85.40281348720606</v>
+        <v>84.43930618226577</v>
       </c>
       <c r="E54">
-        <v>-28.252</v>
+        <v>-26.85299999999999</v>
       </c>
       <c r="F54">
-        <v>72.748</v>
+        <v>74.14700000000001</v>
       </c>
       <c r="G54">
         <v>2.19</v>
@@ -5703,37 +5703,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M54">
-        <v>10.6794064</v>
+        <v>10.8847796</v>
       </c>
       <c r="N54">
-        <v>-1.716073066666667</v>
+        <v>-1.921446266666667</v>
       </c>
       <c r="O54">
-        <v>-0.3946968053333333</v>
+        <v>-0.4419326413333334</v>
       </c>
       <c r="P54">
-        <v>-1.321376261333333</v>
+        <v>-1.479513625333333</v>
       </c>
       <c r="Q54">
-        <v>2.198623738666667</v>
+        <v>2.040486374666667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1514871010477547</v>
+        <v>0.153735762772175</v>
       </c>
       <c r="T54">
-        <v>1.634945840682847</v>
+        <v>1.669731922399504</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1930413161041111</v>
+        <v>0.1893990271210146</v>
       </c>
       <c r="W54">
-        <v>0.1184615347959165</v>
+        <v>0.1189962228186351</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8393100700178742</v>
+        <v>0.8234740309609332</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1353238065967988</v>
+        <v>0.1363338065967988</v>
       </c>
       <c r="C55">
-        <v>12.48230618226576</v>
+        <v>10.14129675562241</v>
       </c>
       <c r="D55">
-        <v>84.43930618226577</v>
+        <v>83.49729675562241</v>
       </c>
       <c r="E55">
-        <v>-26.85299999999999</v>
+        <v>-25.45399999999999</v>
       </c>
       <c r="F55">
-        <v>74.14700000000001</v>
+        <v>75.54600000000001</v>
       </c>
       <c r="G55">
         <v>2.19</v>
@@ -5785,37 +5785,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M55">
-        <v>10.8847796</v>
+        <v>11.0901528</v>
       </c>
       <c r="N55">
-        <v>-1.921446266666667</v>
+        <v>-2.126819466666667</v>
       </c>
       <c r="O55">
-        <v>-0.4419326413333334</v>
+        <v>-0.4891684773333335</v>
       </c>
       <c r="P55">
-        <v>-1.479513625333333</v>
+        <v>-1.637650989333334</v>
       </c>
       <c r="Q55">
-        <v>2.040486374666667</v>
+        <v>1.882349010666666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.153735762772175</v>
+        <v>0.1560821923976571</v>
       </c>
       <c r="T55">
-        <v>1.669731922399504</v>
+        <v>1.706030442451667</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1893990271210146</v>
+        <v>0.1858916377298847</v>
       </c>
       <c r="W55">
-        <v>0.1189962228186351</v>
+        <v>0.1195111075812529</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8234740309609332</v>
+        <v>0.808224511869064</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1363338065967988</v>
+        <v>0.1685660654284778</v>
       </c>
       <c r="C56">
-        <v>10.14129675562241</v>
+        <v>-13.17993779168134</v>
       </c>
       <c r="D56">
-        <v>83.49729675562241</v>
+        <v>61.57506220831867</v>
       </c>
       <c r="E56">
-        <v>-25.45399999999999</v>
+        <v>-24.05499999999999</v>
       </c>
       <c r="F56">
-        <v>75.54600000000001</v>
+        <v>76.94500000000001</v>
       </c>
       <c r="G56">
         <v>2.19</v>
@@ -5867,45 +5867,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M56">
-        <v>11.0901528</v>
+        <v>15.450556</v>
       </c>
       <c r="N56">
-        <v>-2.126819466666667</v>
+        <v>-6.487222666666668</v>
       </c>
       <c r="O56">
-        <v>-0.4891684773333335</v>
+        <v>-1.492061213333334</v>
       </c>
       <c r="P56">
-        <v>-1.637650989333334</v>
+        <v>-4.995161453333334</v>
       </c>
       <c r="Q56">
-        <v>1.882349010666666</v>
+        <v>-1.475161453333334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1560821923976571</v>
+        <v>0.1619157051880026</v>
       </c>
       <c r="T56">
-        <v>1.706030442451667</v>
+        <v>1.796273030038927</v>
       </c>
       <c r="U56">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1858916377298847</v>
+        <v>0.1334299339562063</v>
       </c>
       <c r="W56">
-        <v>0.1195111075812529</v>
+        <v>0.1740072692615938</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.808224511869064</v>
+        <v>0.5801301476356795</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1685660654284778</v>
+        <v>0.1701160654284778</v>
       </c>
       <c r="C57">
-        <v>-13.17993779168134</v>
+        <v>-15.34666918740994</v>
       </c>
       <c r="D57">
-        <v>61.57506220831867</v>
+        <v>60.80733081259007</v>
       </c>
       <c r="E57">
-        <v>-24.05499999999999</v>
+        <v>-22.65599999999999</v>
       </c>
       <c r="F57">
-        <v>76.94500000000001</v>
+        <v>78.34400000000001</v>
       </c>
       <c r="G57">
         <v>2.19</v>
@@ -5949,37 +5949,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M57">
-        <v>15.450556</v>
+        <v>15.7314752</v>
       </c>
       <c r="N57">
-        <v>-6.487222666666668</v>
+        <v>-6.768141866666667</v>
       </c>
       <c r="O57">
-        <v>-1.492061213333334</v>
+        <v>-1.556672629333334</v>
       </c>
       <c r="P57">
-        <v>-4.995161453333334</v>
+        <v>-5.211469237333334</v>
       </c>
       <c r="Q57">
-        <v>-1.475161453333334</v>
+        <v>-1.691469237333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1619157051880026</v>
+        <v>0.1645546984877299</v>
       </c>
       <c r="T57">
-        <v>1.796273030038927</v>
+        <v>1.837097417085266</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1334299339562063</v>
+        <v>0.1310472565641312</v>
       </c>
       <c r="W57">
-        <v>0.1740072692615938</v>
+        <v>0.1744857108819225</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5801301476356795</v>
+        <v>0.5697706807136138</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1701160654284778</v>
+        <v>0.1716660654284777</v>
       </c>
       <c r="C58">
-        <v>-15.34666918740994</v>
+        <v>-17.49449185409662</v>
       </c>
       <c r="D58">
-        <v>60.80733081259007</v>
+        <v>60.05850814590339</v>
       </c>
       <c r="E58">
-        <v>-22.65599999999999</v>
+        <v>-21.25699999999999</v>
       </c>
       <c r="F58">
-        <v>78.34400000000001</v>
+        <v>79.74300000000001</v>
       </c>
       <c r="G58">
         <v>2.19</v>
@@ -6031,37 +6031,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M58">
-        <v>15.7314752</v>
+        <v>16.0123944</v>
       </c>
       <c r="N58">
-        <v>-6.768141866666667</v>
+        <v>-7.049061066666667</v>
       </c>
       <c r="O58">
-        <v>-1.556672629333334</v>
+        <v>-1.621284045333333</v>
       </c>
       <c r="P58">
-        <v>-5.211469237333334</v>
+        <v>-5.427777021333333</v>
       </c>
       <c r="Q58">
-        <v>-1.691469237333334</v>
+        <v>-1.907777021333333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1645546984877299</v>
+        <v>0.1673164356618632</v>
       </c>
       <c r="T58">
-        <v>1.837097417085266</v>
+        <v>1.879820612831435</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1310472565641312</v>
+        <v>0.1287481818875675</v>
       </c>
       <c r="W58">
-        <v>0.1744857108819225</v>
+        <v>0.1749473650769764</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5697706807136138</v>
+        <v>0.559774703858989</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1716660654284777</v>
+        <v>0.1732160654284778</v>
       </c>
       <c r="C59">
-        <v>-17.49449185409662</v>
+        <v>-19.62409585849044</v>
       </c>
       <c r="D59">
-        <v>60.05850814590339</v>
+        <v>59.32790414150957</v>
       </c>
       <c r="E59">
-        <v>-21.25699999999999</v>
+        <v>-19.85799999999999</v>
       </c>
       <c r="F59">
-        <v>79.74300000000001</v>
+        <v>81.14200000000001</v>
       </c>
       <c r="G59">
         <v>2.19</v>
@@ -6113,37 +6113,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M59">
-        <v>16.0123944</v>
+        <v>16.2933136</v>
       </c>
       <c r="N59">
-        <v>-7.049061066666667</v>
+        <v>-7.329980266666666</v>
       </c>
       <c r="O59">
-        <v>-1.621284045333333</v>
+        <v>-1.685895461333333</v>
       </c>
       <c r="P59">
-        <v>-5.427777021333333</v>
+        <v>-5.644084805333333</v>
       </c>
       <c r="Q59">
-        <v>-1.907777021333333</v>
+        <v>-2.124084805333333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1673164356618632</v>
+        <v>0.1702096841300028</v>
       </c>
       <c r="T59">
-        <v>1.879820612831435</v>
+        <v>1.924578246470279</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1287481818875675</v>
+        <v>0.1265283856481267</v>
       </c>
       <c r="W59">
-        <v>0.1749473650769764</v>
+        <v>0.1753931001618562</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.559774703858989</v>
+        <v>0.5501234158614202</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1732160654284778</v>
+        <v>0.1747660654284777</v>
       </c>
       <c r="C60">
-        <v>-19.62409585849044</v>
+        <v>-21.7361380926147</v>
       </c>
       <c r="D60">
-        <v>59.32790414150956</v>
+        <v>58.6148619073853</v>
       </c>
       <c r="E60">
-        <v>-19.858</v>
+        <v>-18.459</v>
       </c>
       <c r="F60">
-        <v>81.142</v>
+        <v>82.541</v>
       </c>
       <c r="G60">
         <v>2.19</v>
@@ -6195,37 +6195,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M60">
-        <v>16.2933136</v>
+        <v>16.5742328</v>
       </c>
       <c r="N60">
-        <v>-7.329980266666666</v>
+        <v>-7.610899466666666</v>
       </c>
       <c r="O60">
-        <v>-1.685895461333333</v>
+        <v>-1.750506877333333</v>
       </c>
       <c r="P60">
-        <v>-5.644084805333333</v>
+        <v>-5.860392589333333</v>
       </c>
       <c r="Q60">
-        <v>-2.124084805333333</v>
+        <v>-2.340392589333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1702096841300028</v>
+        <v>0.1732440666697589</v>
       </c>
       <c r="T60">
-        <v>1.924578246470279</v>
+        <v>1.971519179311017</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1265283856481267</v>
+        <v>0.1243838367388364</v>
       </c>
       <c r="W60">
-        <v>0.1753931001618562</v>
+        <v>0.1758237255828417</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5501234158614202</v>
+        <v>0.5407992901688539</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1747660654284777</v>
+        <v>0.1763160654284777</v>
       </c>
       <c r="C61">
-        <v>-21.7361380926147</v>
+        <v>-23.83124424367114</v>
       </c>
       <c r="D61">
-        <v>58.6148619073853</v>
+        <v>57.91875575632886</v>
       </c>
       <c r="E61">
-        <v>-18.459</v>
+        <v>-17.06</v>
       </c>
       <c r="F61">
-        <v>82.541</v>
+        <v>83.94</v>
       </c>
       <c r="G61">
         <v>2.19</v>
@@ -6277,37 +6277,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M61">
-        <v>16.5742328</v>
+        <v>16.855152</v>
       </c>
       <c r="N61">
-        <v>-7.610899466666666</v>
+        <v>-7.891818666666666</v>
       </c>
       <c r="O61">
-        <v>-1.750506877333333</v>
+        <v>-1.815118293333333</v>
       </c>
       <c r="P61">
-        <v>-5.860392589333333</v>
+        <v>-6.076700373333333</v>
       </c>
       <c r="Q61">
-        <v>-2.340392589333333</v>
+        <v>-2.556700373333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1732440666697589</v>
+        <v>0.1764301683365029</v>
       </c>
       <c r="T61">
-        <v>1.971519179311017</v>
+        <v>2.020807158793792</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1243838367388364</v>
+        <v>0.1223107727931891</v>
       </c>
       <c r="W61">
-        <v>0.1758237255828417</v>
+        <v>0.1762399968231276</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5407992901688539</v>
+        <v>0.5317859686660396</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1763160654284777</v>
+        <v>0.1778660654284778</v>
       </c>
       <c r="C62">
-        <v>-23.83124424367114</v>
+        <v>-25.91001062522455</v>
       </c>
       <c r="D62">
-        <v>57.91875575632886</v>
+        <v>57.23898937477545</v>
       </c>
       <c r="E62">
-        <v>-17.06</v>
+        <v>-15.661</v>
       </c>
       <c r="F62">
-        <v>83.94</v>
+        <v>85.339</v>
       </c>
       <c r="G62">
         <v>2.19</v>
@@ -6359,37 +6359,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M62">
-        <v>16.855152</v>
+        <v>17.1360712</v>
       </c>
       <c r="N62">
-        <v>-7.891818666666666</v>
+        <v>-8.172737866666665</v>
       </c>
       <c r="O62">
-        <v>-1.815118293333333</v>
+        <v>-1.879729709333333</v>
       </c>
       <c r="P62">
-        <v>-6.076700373333333</v>
+        <v>-6.293008157333333</v>
       </c>
       <c r="Q62">
-        <v>-2.556700373333333</v>
+        <v>-2.773008157333333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1764301683365029</v>
+        <v>0.1797796598323107</v>
       </c>
       <c r="T62">
-        <v>2.020807158793792</v>
+        <v>2.072622726967992</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1223107727931891</v>
+        <v>0.1203056781572352</v>
       </c>
       <c r="W62">
-        <v>0.1762399968231276</v>
+        <v>0.1766426198260272</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5317859686660396</v>
+        <v>0.5230681659010226</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1778660654284778</v>
+        <v>0.1794160654284777</v>
       </c>
       <c r="C63">
-        <v>-25.91001062522455</v>
+        <v>-27.97300588093271</v>
       </c>
       <c r="D63">
-        <v>57.23898937477545</v>
+        <v>56.57499411906729</v>
       </c>
       <c r="E63">
-        <v>-15.661</v>
+        <v>-14.262</v>
       </c>
       <c r="F63">
-        <v>85.339</v>
+        <v>86.738</v>
       </c>
       <c r="G63">
         <v>2.19</v>
@@ -6441,37 +6441,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M63">
-        <v>17.1360712</v>
+        <v>17.4169904</v>
       </c>
       <c r="N63">
-        <v>-8.172737866666665</v>
+        <v>-8.453657066666665</v>
       </c>
       <c r="O63">
-        <v>-1.879729709333333</v>
+        <v>-1.944341125333333</v>
       </c>
       <c r="P63">
-        <v>-6.293008157333333</v>
+        <v>-6.509315941333332</v>
       </c>
       <c r="Q63">
-        <v>-2.773008157333333</v>
+        <v>-2.989315941333332</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1797796598323107</v>
+        <v>0.1833054403542136</v>
       </c>
       <c r="T63">
-        <v>2.072622726967992</v>
+        <v>2.127165430309255</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1203056781572352</v>
+        <v>0.1183652639934088</v>
       </c>
       <c r="W63">
-        <v>0.1766426198260272</v>
+        <v>0.1770322549901235</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5230681659010226</v>
+        <v>0.5146315825800383</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1794160654284777</v>
+        <v>0.1809660654284777</v>
       </c>
       <c r="C64">
-        <v>-27.97300588093271</v>
+        <v>-30.02077257105253</v>
       </c>
       <c r="D64">
-        <v>56.57499411906729</v>
+        <v>55.92622742894747</v>
       </c>
       <c r="E64">
-        <v>-14.262</v>
+        <v>-12.863</v>
       </c>
       <c r="F64">
-        <v>86.738</v>
+        <v>88.137</v>
       </c>
       <c r="G64">
         <v>2.19</v>
@@ -6523,37 +6523,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M64">
-        <v>17.4169904</v>
+        <v>17.6979096</v>
       </c>
       <c r="N64">
-        <v>-8.453657066666665</v>
+        <v>-8.734576266666664</v>
       </c>
       <c r="O64">
-        <v>-1.944341125333333</v>
+        <v>-2.008952541333333</v>
       </c>
       <c r="P64">
-        <v>-6.509315941333332</v>
+        <v>-6.725623725333332</v>
       </c>
       <c r="Q64">
-        <v>-2.989315941333332</v>
+        <v>-3.205623725333332</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1833054403542136</v>
+        <v>0.1870218036070302</v>
       </c>
       <c r="T64">
-        <v>2.127165430309255</v>
+        <v>2.184656387885181</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1183652639934088</v>
+        <v>0.1164864502792277</v>
       </c>
       <c r="W64">
-        <v>0.1770322549901235</v>
+        <v>0.1774095207839311</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5146315825800383</v>
+        <v>0.5064628273009901</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1809660654284777</v>
+        <v>0.2055303152539078</v>
       </c>
       <c r="C65">
-        <v>-30.02077257105253</v>
+        <v>-40.0204306250651</v>
       </c>
       <c r="D65">
-        <v>55.92622742894747</v>
+        <v>47.3255693749349</v>
       </c>
       <c r="E65">
-        <v>-12.863</v>
+        <v>-11.464</v>
       </c>
       <c r="F65">
-        <v>88.137</v>
+        <v>89.536</v>
       </c>
       <c r="G65">
         <v>2.19</v>
@@ -6605,45 +6605,45 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M65">
-        <v>17.6979096</v>
+        <v>21.1125888</v>
       </c>
       <c r="N65">
-        <v>-8.734576266666664</v>
+        <v>-12.14925546666667</v>
       </c>
       <c r="O65">
-        <v>-2.008952541333333</v>
+        <v>-2.794328757333334</v>
       </c>
       <c r="P65">
-        <v>-6.725623725333332</v>
+        <v>-9.354926709333332</v>
       </c>
       <c r="Q65">
-        <v>-3.205623725333332</v>
+        <v>-5.834926709333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1870218036070302</v>
+        <v>0.1926508810000868</v>
       </c>
       <c r="T65">
-        <v>2.184656387885181</v>
+        <v>2.271736424894629</v>
       </c>
       <c r="U65">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1164864502792277</v>
+        <v>0.09764632306326484</v>
       </c>
       <c r="W65">
-        <v>0.1774095207839311</v>
+        <v>0.2127749970216822</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.5064628273009901</v>
+        <v>0.4245492307098471</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2055303152539078</v>
+        <v>0.2074303152539078</v>
       </c>
       <c r="C66">
-        <v>-40.0204306250651</v>
+        <v>-41.97575312973336</v>
       </c>
       <c r="D66">
-        <v>47.3255693749349</v>
+        <v>46.76924687026664</v>
       </c>
       <c r="E66">
-        <v>-11.464</v>
+        <v>-10.065</v>
       </c>
       <c r="F66">
-        <v>89.536</v>
+        <v>90.935</v>
       </c>
       <c r="G66">
         <v>2.19</v>
@@ -6687,37 +6687,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M66">
-        <v>21.1125888</v>
+        <v>21.442473</v>
       </c>
       <c r="N66">
-        <v>-12.14925546666667</v>
+        <v>-12.47913966666666</v>
       </c>
       <c r="O66">
-        <v>-2.794328757333334</v>
+        <v>-2.870202123333333</v>
       </c>
       <c r="P66">
-        <v>-9.354926709333332</v>
+        <v>-9.608937543333331</v>
       </c>
       <c r="Q66">
-        <v>-5.834926709333333</v>
+        <v>-6.088937543333332</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1926508810000868</v>
+        <v>0.1968466204572321</v>
       </c>
       <c r="T66">
-        <v>2.271736424894629</v>
+        <v>2.336643179891619</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09764632306326484</v>
+        <v>0.09614407193921462</v>
       </c>
       <c r="W66">
-        <v>0.2127749970216822</v>
+        <v>0.2131292278367332</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4245492307098471</v>
+        <v>0.4180177040835418</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2074303152539078</v>
+        <v>0.2093303152539078</v>
       </c>
       <c r="C67">
-        <v>-41.97575312973336</v>
+        <v>-43.91814821165157</v>
       </c>
       <c r="D67">
-        <v>46.76924687026664</v>
+        <v>46.22585178834844</v>
       </c>
       <c r="E67">
-        <v>-10.065</v>
+        <v>-8.665999999999997</v>
       </c>
       <c r="F67">
-        <v>90.935</v>
+        <v>92.334</v>
       </c>
       <c r="G67">
         <v>2.19</v>
@@ -6769,37 +6769,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M67">
-        <v>21.442473</v>
+        <v>21.7723572</v>
       </c>
       <c r="N67">
-        <v>-12.47913966666666</v>
+        <v>-12.80902386666667</v>
       </c>
       <c r="O67">
-        <v>-2.870202123333333</v>
+        <v>-2.946075489333333</v>
       </c>
       <c r="P67">
-        <v>-9.608937543333331</v>
+        <v>-9.862948377333334</v>
       </c>
       <c r="Q67">
-        <v>-6.088937543333332</v>
+        <v>-6.342948377333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1968466204572321</v>
+        <v>0.2012891681177389</v>
       </c>
       <c r="T67">
-        <v>2.336643179891619</v>
+        <v>2.405367979300195</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09614407193921462</v>
+        <v>0.09468734357649923</v>
       </c>
       <c r="W67">
-        <v>0.2131292278367332</v>
+        <v>0.2134727243846615</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4180177040835418</v>
+        <v>0.4116841025065184</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2093303152539078</v>
+        <v>0.2112303152539078</v>
       </c>
       <c r="C68">
-        <v>-43.91814821165157</v>
+        <v>-45.84806129286682</v>
       </c>
       <c r="D68">
-        <v>46.22585178834844</v>
+        <v>45.69493870713319</v>
       </c>
       <c r="E68">
-        <v>-8.665999999999997</v>
+        <v>-7.266999999999996</v>
       </c>
       <c r="F68">
-        <v>92.334</v>
+        <v>93.733</v>
       </c>
       <c r="G68">
         <v>2.19</v>
@@ -6851,37 +6851,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M68">
-        <v>21.7723572</v>
+        <v>22.1022414</v>
       </c>
       <c r="N68">
-        <v>-12.80902386666667</v>
+        <v>-13.13890806666667</v>
       </c>
       <c r="O68">
-        <v>-2.946075489333333</v>
+        <v>-3.021948855333333</v>
       </c>
       <c r="P68">
-        <v>-9.862948377333334</v>
+        <v>-10.11695921133333</v>
       </c>
       <c r="Q68">
-        <v>-6.342948377333334</v>
+        <v>-6.596959211333333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2012891681177389</v>
+        <v>0.2060009610910038</v>
       </c>
       <c r="T68">
-        <v>2.405367979300195</v>
+        <v>2.478257918066868</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09468734357649923</v>
+        <v>0.09327409964252163</v>
       </c>
       <c r="W68">
-        <v>0.2134727243846615</v>
+        <v>0.2138059673042934</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4116841025065184</v>
+        <v>0.4055395636631376</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2112303152539078</v>
+        <v>0.2131303152539078</v>
       </c>
       <c r="C69">
-        <v>-45.84806129286682</v>
+        <v>-47.76591756473729</v>
       </c>
       <c r="D69">
-        <v>45.69493870713319</v>
+        <v>45.17608243526272</v>
       </c>
       <c r="E69">
-        <v>-7.266999999999996</v>
+        <v>-5.867999999999995</v>
       </c>
       <c r="F69">
-        <v>93.733</v>
+        <v>95.13200000000001</v>
       </c>
       <c r="G69">
         <v>2.19</v>
@@ -6933,37 +6933,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M69">
-        <v>22.1022414</v>
+        <v>22.4321256</v>
       </c>
       <c r="N69">
-        <v>-13.13890806666667</v>
+        <v>-13.46879226666667</v>
       </c>
       <c r="O69">
-        <v>-3.021948855333333</v>
+        <v>-3.097822221333334</v>
       </c>
       <c r="P69">
-        <v>-10.11695921133333</v>
+        <v>-10.37097004533333</v>
       </c>
       <c r="Q69">
-        <v>-6.596959211333333</v>
+        <v>-6.850970045333334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2060009610910038</v>
+        <v>0.2110072411250977</v>
       </c>
       <c r="T69">
-        <v>2.478257918066868</v>
+        <v>2.555703478006458</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09327409964252163</v>
+        <v>0.09190242170660219</v>
       </c>
       <c r="W69">
-        <v>0.2138059673042934</v>
+        <v>0.2141294089615832</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4055395636631376</v>
+        <v>0.3995757465504444</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2131303152539078</v>
+        <v>0.2150303152539078</v>
       </c>
       <c r="C70">
-        <v>-47.76591756473729</v>
+        <v>-49.67212312361259</v>
       </c>
       <c r="D70">
-        <v>45.17608243526272</v>
+        <v>44.66887687638742</v>
       </c>
       <c r="E70">
-        <v>-5.867999999999995</v>
+        <v>-4.468999999999994</v>
       </c>
       <c r="F70">
-        <v>95.13200000000001</v>
+        <v>96.53100000000001</v>
       </c>
       <c r="G70">
         <v>2.19</v>
@@ -7015,37 +7015,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M70">
-        <v>22.4321256</v>
+        <v>22.7620098</v>
       </c>
       <c r="N70">
-        <v>-13.46879226666667</v>
+        <v>-13.79867646666667</v>
       </c>
       <c r="O70">
-        <v>-3.097822221333334</v>
+        <v>-3.173695587333333</v>
       </c>
       <c r="P70">
-        <v>-10.37097004533333</v>
+        <v>-10.62498087933333</v>
       </c>
       <c r="Q70">
-        <v>-6.850970045333334</v>
+        <v>-7.104980879333333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2110072411250977</v>
+        <v>0.2163365069678428</v>
       </c>
       <c r="T70">
-        <v>2.555703478006458</v>
+        <v>2.638145525684086</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09190242170660219</v>
+        <v>0.09057050255143406</v>
       </c>
       <c r="W70">
-        <v>0.2141294089615832</v>
+        <v>0.2144434754983719</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3995757465504444</v>
+        <v>0.3937847937018871</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2150303152539078</v>
+        <v>0.2169303152539079</v>
       </c>
       <c r="C71">
-        <v>-49.67212312361259</v>
+        <v>-51.56706603085968</v>
       </c>
       <c r="D71">
-        <v>44.66887687638742</v>
+        <v>44.17293396914033</v>
       </c>
       <c r="E71">
-        <v>-4.468999999999994</v>
+        <v>-3.069999999999993</v>
       </c>
       <c r="F71">
-        <v>96.53100000000001</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="G71">
         <v>2.19</v>
@@ -7097,37 +7097,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M71">
-        <v>22.7620098</v>
+        <v>23.091894</v>
       </c>
       <c r="N71">
-        <v>-13.79867646666667</v>
+        <v>-14.12856066666667</v>
       </c>
       <c r="O71">
-        <v>-3.173695587333333</v>
+        <v>-3.249568953333334</v>
       </c>
       <c r="P71">
-        <v>-10.62498087933333</v>
+        <v>-10.87899171333333</v>
       </c>
       <c r="Q71">
-        <v>-7.104980879333333</v>
+        <v>-7.358991713333335</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2163365069678428</v>
+        <v>0.2220210572001042</v>
       </c>
       <c r="T71">
-        <v>2.638145525684086</v>
+        <v>2.726083709873555</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09057050255143406</v>
+        <v>0.08927663822927071</v>
       </c>
       <c r="W71">
-        <v>0.2144434754983719</v>
+        <v>0.214748568705538</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3937847937018871</v>
+        <v>0.3881592966490031</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2169303152539079</v>
+        <v>0.2188303152539078</v>
       </c>
       <c r="C72">
-        <v>-51.56706603085968</v>
+        <v>-53.45111730304981</v>
       </c>
       <c r="D72">
-        <v>44.17293396914033</v>
+        <v>43.6878826969502</v>
       </c>
       <c r="E72">
-        <v>-3.069999999999993</v>
+        <v>-1.670999999999992</v>
       </c>
       <c r="F72">
-        <v>97.93000000000001</v>
+        <v>99.32900000000001</v>
       </c>
       <c r="G72">
         <v>2.19</v>
@@ -7179,37 +7179,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M72">
-        <v>23.091894</v>
+        <v>23.4217782</v>
       </c>
       <c r="N72">
-        <v>-14.12856066666667</v>
+        <v>-14.45844486666667</v>
       </c>
       <c r="O72">
-        <v>-3.249568953333334</v>
+        <v>-3.325442319333334</v>
       </c>
       <c r="P72">
-        <v>-10.87899171333333</v>
+        <v>-11.13300254733333</v>
       </c>
       <c r="Q72">
-        <v>-7.358991713333335</v>
+        <v>-7.613002547333334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2220210572001042</v>
+        <v>0.2280976453794181</v>
       </c>
       <c r="T72">
-        <v>2.726083709873555</v>
+        <v>2.820086596420919</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08927663822927071</v>
+        <v>0.08801922078942183</v>
       </c>
       <c r="W72">
-        <v>0.214748568705538</v>
+        <v>0.2150450677378543</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3881592966490031</v>
+        <v>0.382692264301834</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2188303152539078</v>
+        <v>0.2207303152539078</v>
       </c>
       <c r="C73">
-        <v>-53.45111730304979</v>
+        <v>-55.32463183761586</v>
       </c>
       <c r="D73">
-        <v>43.6878826969502</v>
+        <v>43.21336816238414</v>
       </c>
       <c r="E73">
-        <v>-1.671000000000006</v>
+        <v>-0.2720000000000056</v>
       </c>
       <c r="F73">
-        <v>99.32899999999999</v>
+        <v>100.728</v>
       </c>
       <c r="G73">
         <v>2.19</v>
@@ -7261,37 +7261,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M73">
-        <v>23.4217782</v>
+        <v>23.7516624</v>
       </c>
       <c r="N73">
-        <v>-14.45844486666666</v>
+        <v>-14.78832906666667</v>
       </c>
       <c r="O73">
-        <v>-3.325442319333333</v>
+        <v>-3.401315685333334</v>
       </c>
       <c r="P73">
-        <v>-11.13300254733333</v>
+        <v>-11.38701338133333</v>
       </c>
       <c r="Q73">
-        <v>-7.61300254733333</v>
+        <v>-7.867013381333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2280976453794181</v>
+        <v>0.2346082755715401</v>
       </c>
       <c r="T73">
-        <v>2.820086596420918</v>
+        <v>2.920803974864522</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08801922078942184</v>
+        <v>0.08679673161179098</v>
       </c>
       <c r="W73">
-        <v>0.2150450677378543</v>
+        <v>0.2153333306859397</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3826922643018341</v>
+        <v>0.3773770939643085</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2207303152539078</v>
+        <v>0.2226303152539078</v>
       </c>
       <c r="C74">
-        <v>-55.32463183761586</v>
+        <v>-57.18794927883423</v>
       </c>
       <c r="D74">
-        <v>43.21336816238414</v>
+        <v>42.74905072116577</v>
       </c>
       <c r="E74">
-        <v>-0.2720000000000056</v>
+        <v>1.126999999999995</v>
       </c>
       <c r="F74">
-        <v>100.728</v>
+        <v>102.127</v>
       </c>
       <c r="G74">
         <v>2.19</v>
@@ -7343,37 +7343,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M74">
-        <v>23.7516624</v>
+        <v>24.0815466</v>
       </c>
       <c r="N74">
-        <v>-14.78832906666667</v>
+        <v>-15.11821326666666</v>
       </c>
       <c r="O74">
-        <v>-3.401315685333334</v>
+        <v>-3.477189051333333</v>
       </c>
       <c r="P74">
-        <v>-11.38701338133333</v>
+        <v>-11.64102421533333</v>
       </c>
       <c r="Q74">
-        <v>-7.867013381333333</v>
+        <v>-8.121024215333332</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2346082755715401</v>
+        <v>0.2416011746667824</v>
       </c>
       <c r="T74">
-        <v>2.920803974864522</v>
+        <v>3.028981899859505</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08679673161179098</v>
+        <v>0.08560773528834179</v>
       </c>
       <c r="W74">
-        <v>0.2153333306859397</v>
+        <v>0.215613696019009</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3773770939643085</v>
+        <v>0.3722075447319207</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2226303152539078</v>
+        <v>0.2245303152539078</v>
       </c>
       <c r="C75">
-        <v>-57.18794927883423</v>
+        <v>-59.04139482857114</v>
       </c>
       <c r="D75">
-        <v>42.74905072116577</v>
+        <v>42.29460517142886</v>
       </c>
       <c r="E75">
-        <v>1.126999999999995</v>
+        <v>2.525999999999996</v>
       </c>
       <c r="F75">
-        <v>102.127</v>
+        <v>103.526</v>
       </c>
       <c r="G75">
         <v>2.19</v>
@@ -7425,37 +7425,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M75">
-        <v>24.0815466</v>
+        <v>24.4114308</v>
       </c>
       <c r="N75">
-        <v>-15.11821326666666</v>
+        <v>-15.44809746666667</v>
       </c>
       <c r="O75">
-        <v>-3.477189051333333</v>
+        <v>-3.553062417333333</v>
       </c>
       <c r="P75">
-        <v>-11.64102421533333</v>
+        <v>-11.89503504933333</v>
       </c>
       <c r="Q75">
-        <v>-8.121024215333332</v>
+        <v>-8.375035049333334</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2416011746667824</v>
+        <v>0.2491319890770432</v>
       </c>
       <c r="T75">
-        <v>3.028981899859505</v>
+        <v>3.145481203700255</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08560773528834179</v>
+        <v>0.08445087400066148</v>
       </c>
       <c r="W75">
-        <v>0.215613696019009</v>
+        <v>0.215886483910644</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3722075447319207</v>
+        <v>0.3671777130463543</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2245303152539078</v>
+        <v>0.2264303152539078</v>
       </c>
       <c r="C76">
-        <v>-59.04139482857114</v>
+        <v>-60.88528000586133</v>
       </c>
       <c r="D76">
-        <v>42.29460517142886</v>
+        <v>41.84971999413868</v>
       </c>
       <c r="E76">
-        <v>2.525999999999996</v>
+        <v>3.925000000000011</v>
       </c>
       <c r="F76">
-        <v>103.526</v>
+        <v>104.925</v>
       </c>
       <c r="G76">
         <v>2.19</v>
@@ -7507,37 +7507,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M76">
-        <v>24.4114308</v>
+        <v>24.741315</v>
       </c>
       <c r="N76">
-        <v>-15.44809746666667</v>
+        <v>-15.77798166666667</v>
       </c>
       <c r="O76">
-        <v>-3.553062417333333</v>
+        <v>-3.628935783333334</v>
       </c>
       <c r="P76">
-        <v>-11.89503504933333</v>
+        <v>-12.14904588333333</v>
       </c>
       <c r="Q76">
-        <v>-8.375035049333334</v>
+        <v>-8.629045883333335</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2491319890770432</v>
+        <v>0.2572652686401249</v>
       </c>
       <c r="T76">
-        <v>3.145481203700255</v>
+        <v>3.271300451848266</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08445087400066148</v>
+        <v>0.08332486234731933</v>
       </c>
       <c r="W76">
-        <v>0.215886483910644</v>
+        <v>0.2161519974585021</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3671777130463543</v>
+        <v>0.3622820102057361</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2264303152539078</v>
+        <v>0.2283303152539078</v>
       </c>
       <c r="C77">
-        <v>-60.88528000586133</v>
+        <v>-62.71990335904656</v>
       </c>
       <c r="D77">
-        <v>41.84971999413868</v>
+        <v>41.41409664095345</v>
       </c>
       <c r="E77">
-        <v>3.925000000000011</v>
+        <v>5.324000000000012</v>
       </c>
       <c r="F77">
-        <v>104.925</v>
+        <v>106.324</v>
       </c>
       <c r="G77">
         <v>2.19</v>
@@ -7589,37 +7589,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M77">
-        <v>24.741315</v>
+        <v>25.0711992</v>
       </c>
       <c r="N77">
-        <v>-15.77798166666667</v>
+        <v>-16.10786586666667</v>
       </c>
       <c r="O77">
-        <v>-3.628935783333334</v>
+        <v>-3.704809149333334</v>
       </c>
       <c r="P77">
-        <v>-12.14904588333333</v>
+        <v>-12.40305671733333</v>
       </c>
       <c r="Q77">
-        <v>-8.629045883333335</v>
+        <v>-8.883056717333334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2572652686401249</v>
+        <v>0.2660763215001302</v>
       </c>
       <c r="T77">
-        <v>3.271300451848266</v>
+        <v>3.407604637341944</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08332486234731933</v>
+        <v>0.08222848257959144</v>
       </c>
       <c r="W77">
-        <v>0.2161519974585021</v>
+        <v>0.2164105238077323</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3622820102057361</v>
+        <v>0.3575151416503975</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2283303152539078</v>
+        <v>0.2302303152539078</v>
       </c>
       <c r="C78">
-        <v>-62.71990335904656</v>
+        <v>-64.54555113389573</v>
       </c>
       <c r="D78">
-        <v>41.41409664095345</v>
+        <v>40.98744886610429</v>
       </c>
       <c r="E78">
-        <v>5.324000000000012</v>
+        <v>6.723000000000013</v>
       </c>
       <c r="F78">
-        <v>106.324</v>
+        <v>107.723</v>
       </c>
       <c r="G78">
         <v>2.19</v>
@@ -7671,37 +7671,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M78">
-        <v>25.0711992</v>
+        <v>25.4010834</v>
       </c>
       <c r="N78">
-        <v>-16.10786586666667</v>
+        <v>-16.43775006666667</v>
       </c>
       <c r="O78">
-        <v>-3.704809149333334</v>
+        <v>-3.780682515333334</v>
       </c>
       <c r="P78">
-        <v>-12.40305671733333</v>
+        <v>-12.65706755133334</v>
       </c>
       <c r="Q78">
-        <v>-8.883056717333334</v>
+        <v>-9.137067551333336</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2660763215001302</v>
+        <v>0.2756535528697011</v>
       </c>
       <c r="T78">
-        <v>3.407604637341944</v>
+        <v>3.555761360704637</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08222848257959144</v>
+        <v>0.08116058020842791</v>
       </c>
       <c r="W78">
-        <v>0.2164105238077323</v>
+        <v>0.2166623351868527</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3575151416503975</v>
+        <v>0.3528720878627301</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2302303152539078</v>
+        <v>0.2321303152539078</v>
       </c>
       <c r="C79">
-        <v>-64.54555113389573</v>
+        <v>-66.36249790084818</v>
       </c>
       <c r="D79">
-        <v>40.98744886610429</v>
+        <v>40.56950209915184</v>
       </c>
       <c r="E79">
-        <v>6.723000000000013</v>
+        <v>8.122000000000014</v>
       </c>
       <c r="F79">
-        <v>107.723</v>
+        <v>109.122</v>
       </c>
       <c r="G79">
         <v>2.19</v>
@@ -7753,37 +7753,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M79">
-        <v>25.4010834</v>
+        <v>25.7309676</v>
       </c>
       <c r="N79">
-        <v>-16.43775006666667</v>
+        <v>-16.76763426666667</v>
       </c>
       <c r="O79">
-        <v>-3.780682515333334</v>
+        <v>-3.856555881333334</v>
       </c>
       <c r="P79">
-        <v>-12.65706755133334</v>
+        <v>-12.91107838533333</v>
       </c>
       <c r="Q79">
-        <v>-9.137067551333336</v>
+        <v>-9.391078385333335</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2756535528697011</v>
+        <v>0.2861014416365056</v>
       </c>
       <c r="T79">
-        <v>3.555761360704637</v>
+        <v>3.717386877100302</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08116058020842791</v>
+        <v>0.08012005994934551</v>
       </c>
       <c r="W79">
-        <v>0.2166623351868527</v>
+        <v>0.2169076898639443</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3528720878627301</v>
+        <v>0.3483480867362848</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2321303152539078</v>
+        <v>0.2340303152539079</v>
       </c>
       <c r="C80">
-        <v>-66.36249790084818</v>
+        <v>-68.17100714426846</v>
       </c>
       <c r="D80">
-        <v>40.56950209915184</v>
+        <v>40.15999285573156</v>
       </c>
       <c r="E80">
-        <v>8.122000000000014</v>
+        <v>9.521000000000015</v>
       </c>
       <c r="F80">
-        <v>109.122</v>
+        <v>110.521</v>
       </c>
       <c r="G80">
         <v>2.19</v>
@@ -7835,37 +7835,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M80">
-        <v>25.7309676</v>
+        <v>26.06085180000001</v>
       </c>
       <c r="N80">
-        <v>-16.76763426666667</v>
+        <v>-17.09751846666667</v>
       </c>
       <c r="O80">
-        <v>-3.856555881333334</v>
+        <v>-3.932429247333334</v>
       </c>
       <c r="P80">
-        <v>-12.91107838533333</v>
+        <v>-13.16508921933334</v>
       </c>
       <c r="Q80">
-        <v>-9.391078385333335</v>
+        <v>-9.645089219333336</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2861014416365056</v>
+        <v>0.2975443674287203</v>
       </c>
       <c r="T80">
-        <v>3.717386877100302</v>
+        <v>3.894405299819364</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08012005994934551</v>
+        <v>0.07910588197530315</v>
       </c>
       <c r="W80">
-        <v>0.2169076898639443</v>
+        <v>0.2171468330302235</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3483480867362848</v>
+        <v>0.3439386172839267</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2340303152539079</v>
+        <v>0.2359303152539078</v>
       </c>
       <c r="C81">
-        <v>-68.17100714426846</v>
+        <v>-69.97133181637027</v>
       </c>
       <c r="D81">
-        <v>40.15999285573156</v>
+        <v>39.75866818362975</v>
       </c>
       <c r="E81">
-        <v>9.521000000000015</v>
+        <v>10.92000000000002</v>
       </c>
       <c r="F81">
-        <v>110.521</v>
+        <v>111.92</v>
       </c>
       <c r="G81">
         <v>2.19</v>
@@ -7917,37 +7917,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M81">
-        <v>26.06085180000001</v>
+        <v>26.390736</v>
       </c>
       <c r="N81">
-        <v>-17.09751846666667</v>
+        <v>-17.42740266666667</v>
       </c>
       <c r="O81">
-        <v>-3.932429247333334</v>
+        <v>-4.008302613333334</v>
       </c>
       <c r="P81">
-        <v>-13.16508921933334</v>
+        <v>-13.41910005333333</v>
       </c>
       <c r="Q81">
-        <v>-9.645089219333336</v>
+        <v>-9.899100053333335</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2975443674287203</v>
+        <v>0.3101315858001563</v>
       </c>
       <c r="T81">
-        <v>3.894405299819364</v>
+        <v>4.089125564810333</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07910588197530315</v>
+        <v>0.07811705845061187</v>
       </c>
       <c r="W81">
-        <v>0.2171468330302235</v>
+        <v>0.2173799976173457</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3439386172839267</v>
+        <v>0.3396393845678777</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2359303152539078</v>
+        <v>0.2378303152539079</v>
       </c>
       <c r="C82">
-        <v>-69.97133181637027</v>
+        <v>-71.76371485825621</v>
       </c>
       <c r="D82">
-        <v>39.75866818362975</v>
+        <v>39.36528514174381</v>
       </c>
       <c r="E82">
-        <v>10.92000000000002</v>
+        <v>12.31900000000002</v>
       </c>
       <c r="F82">
-        <v>111.92</v>
+        <v>113.319</v>
       </c>
       <c r="G82">
         <v>2.19</v>
@@ -7999,37 +7999,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M82">
-        <v>26.390736</v>
+        <v>26.72062020000001</v>
       </c>
       <c r="N82">
-        <v>-17.42740266666667</v>
+        <v>-17.75728686666667</v>
       </c>
       <c r="O82">
-        <v>-4.008302613333334</v>
+        <v>-4.084175979333335</v>
       </c>
       <c r="P82">
-        <v>-13.41910005333333</v>
+        <v>-13.67311088733334</v>
       </c>
       <c r="Q82">
-        <v>-9.899100053333335</v>
+        <v>-10.15311088733334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3101315858001563</v>
+        <v>0.3240437745264803</v>
       </c>
       <c r="T82">
-        <v>4.089125564810333</v>
+        <v>4.304342699800351</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07811705845061187</v>
+        <v>0.07715265032159196</v>
       </c>
       <c r="W82">
-        <v>0.2173799976173457</v>
+        <v>0.2176074050541686</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3396393845678777</v>
+        <v>0.3354463057460519</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2378303152539079</v>
+        <v>0.2397303152539078</v>
       </c>
       <c r="C83">
-        <v>-71.76371485825621</v>
+        <v>-73.54838969032869</v>
       </c>
       <c r="D83">
-        <v>39.36528514174381</v>
+        <v>38.97961030967134</v>
       </c>
       <c r="E83">
-        <v>12.31900000000002</v>
+        <v>13.71800000000002</v>
       </c>
       <c r="F83">
-        <v>113.319</v>
+        <v>114.718</v>
       </c>
       <c r="G83">
         <v>2.19</v>
@@ -8081,37 +8081,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M83">
-        <v>26.72062020000001</v>
+        <v>27.0505044</v>
       </c>
       <c r="N83">
-        <v>-17.75728686666667</v>
+        <v>-18.08717106666667</v>
       </c>
       <c r="O83">
-        <v>-4.084175979333335</v>
+        <v>-4.160049345333334</v>
       </c>
       <c r="P83">
-        <v>-13.67311088733334</v>
+        <v>-13.92712172133334</v>
       </c>
       <c r="Q83">
-        <v>-10.15311088733334</v>
+        <v>-10.40712172133334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3240437745264803</v>
+        <v>0.3395017620001736</v>
       </c>
       <c r="T83">
-        <v>4.304342699800351</v>
+        <v>4.543472849789259</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07715265032159196</v>
+        <v>0.07621176434206035</v>
       </c>
       <c r="W83">
-        <v>0.2176074050541686</v>
+        <v>0.2178292659681422</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3354463057460519</v>
+        <v>0.3313554971393928</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2397303152539078</v>
+        <v>0.2416303152539078</v>
       </c>
       <c r="C84">
-        <v>-73.54838969032869</v>
+        <v>-75.32558067415236</v>
       </c>
       <c r="D84">
-        <v>38.97961030967134</v>
+        <v>38.60141932584766</v>
       </c>
       <c r="E84">
-        <v>13.71800000000002</v>
+        <v>15.11700000000002</v>
       </c>
       <c r="F84">
-        <v>114.718</v>
+        <v>116.117</v>
       </c>
       <c r="G84">
         <v>2.19</v>
@@ -8163,37 +8163,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M84">
-        <v>27.0505044</v>
+        <v>27.38038860000001</v>
       </c>
       <c r="N84">
-        <v>-18.08717106666667</v>
+        <v>-18.41705526666667</v>
       </c>
       <c r="O84">
-        <v>-4.160049345333334</v>
+        <v>-4.235922711333335</v>
       </c>
       <c r="P84">
-        <v>-13.92712172133334</v>
+        <v>-14.18113255533334</v>
       </c>
       <c r="Q84">
-        <v>-10.40712172133334</v>
+        <v>-10.66113255533334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3395017620001736</v>
+        <v>0.356778336235478</v>
       </c>
       <c r="T84">
-        <v>4.543472849789259</v>
+        <v>4.810735958600392</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07621176434206035</v>
+        <v>0.07529355031384274</v>
       </c>
       <c r="W84">
-        <v>0.2178292659681422</v>
+        <v>0.2180457808359959</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3313554971393928</v>
+        <v>0.327363262234099</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2416303152539078</v>
+        <v>0.2435303152539078</v>
       </c>
       <c r="C85">
-        <v>-75.32558067415236</v>
+        <v>-77.09550354768811</v>
       </c>
       <c r="D85">
-        <v>38.60141932584766</v>
+        <v>38.23049645231191</v>
       </c>
       <c r="E85">
-        <v>15.11700000000002</v>
+        <v>16.51600000000002</v>
       </c>
       <c r="F85">
-        <v>116.117</v>
+        <v>117.516</v>
       </c>
       <c r="G85">
         <v>2.19</v>
@@ -8245,37 +8245,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M85">
-        <v>27.38038860000001</v>
+        <v>27.71027280000001</v>
       </c>
       <c r="N85">
-        <v>-18.41705526666667</v>
+        <v>-18.74693946666667</v>
       </c>
       <c r="O85">
-        <v>-4.235922711333335</v>
+        <v>-4.311796077333335</v>
       </c>
       <c r="P85">
-        <v>-14.18113255533334</v>
+        <v>-14.43514338933334</v>
       </c>
       <c r="Q85">
-        <v>-10.66113255533334</v>
+        <v>-10.91514338933334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.356778336235478</v>
+        <v>0.3762144822501954</v>
       </c>
       <c r="T85">
-        <v>4.810735958600392</v>
+        <v>5.111406956012917</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07529355031384274</v>
+        <v>0.07439719852439225</v>
       </c>
       <c r="W85">
-        <v>0.2180457808359959</v>
+        <v>0.2182571405879483</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.327363262234099</v>
+        <v>0.3234660805408358</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2435303152539078</v>
+        <v>0.2454303152539078</v>
       </c>
       <c r="C86">
-        <v>-77.09550354768808</v>
+        <v>-78.85836583567279</v>
       </c>
       <c r="D86">
-        <v>38.23049645231193</v>
+        <v>37.86663416432722</v>
       </c>
       <c r="E86">
-        <v>16.51600000000001</v>
+        <v>17.91500000000001</v>
       </c>
       <c r="F86">
-        <v>117.516</v>
+        <v>118.915</v>
       </c>
       <c r="G86">
         <v>2.19</v>
@@ -8327,37 +8327,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M86">
-        <v>27.7102728</v>
+        <v>28.040157</v>
       </c>
       <c r="N86">
-        <v>-18.74693946666667</v>
+        <v>-19.07682366666667</v>
       </c>
       <c r="O86">
-        <v>-4.311796077333334</v>
+        <v>-4.387669443333334</v>
       </c>
       <c r="P86">
-        <v>-14.43514338933333</v>
+        <v>-14.68915422333334</v>
       </c>
       <c r="Q86">
-        <v>-10.91514338933333</v>
+        <v>-11.16915422333334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3762144822501952</v>
+        <v>0.3982421144002082</v>
       </c>
       <c r="T86">
-        <v>5.111406956012914</v>
+        <v>5.452167419747108</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07439719852439225</v>
+        <v>0.07352193736528176</v>
       </c>
       <c r="W86">
-        <v>0.2182571405879483</v>
+        <v>0.2184635271692666</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3234660805408359</v>
+        <v>0.3196605972403554</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2454303152539078</v>
+        <v>0.2473303152539078</v>
       </c>
       <c r="C87">
-        <v>-78.85836583567279</v>
+        <v>-80.61436723678496</v>
       </c>
       <c r="D87">
-        <v>37.86663416432722</v>
+        <v>37.50963276321505</v>
       </c>
       <c r="E87">
-        <v>17.91500000000001</v>
+        <v>19.31400000000001</v>
       </c>
       <c r="F87">
-        <v>118.915</v>
+        <v>120.314</v>
       </c>
       <c r="G87">
         <v>2.19</v>
@@ -8409,37 +8409,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M87">
-        <v>28.040157</v>
+        <v>28.3700412</v>
       </c>
       <c r="N87">
-        <v>-19.07682366666667</v>
+        <v>-19.40670786666667</v>
       </c>
       <c r="O87">
-        <v>-4.387669443333334</v>
+        <v>-4.463542809333334</v>
       </c>
       <c r="P87">
-        <v>-14.68915422333334</v>
+        <v>-14.94316505733333</v>
       </c>
       <c r="Q87">
-        <v>-11.16915422333334</v>
+        <v>-11.42316505733334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3982421144002082</v>
+        <v>0.4234165511430802</v>
       </c>
       <c r="T87">
-        <v>5.452167419747108</v>
+        <v>5.841607949729045</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07352193736528176</v>
+        <v>0.07266703111684825</v>
       </c>
       <c r="W87">
-        <v>0.2184635271692666</v>
+        <v>0.2186651140626472</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3196605972403554</v>
+        <v>0.3159436135515141</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2473303152539078</v>
+        <v>0.2492303152539078</v>
       </c>
       <c r="C88">
-        <v>-80.61436723678496</v>
+        <v>-82.36369998911422</v>
       </c>
       <c r="D88">
-        <v>37.50963276321505</v>
+        <v>37.15930001088579</v>
       </c>
       <c r="E88">
-        <v>19.31400000000001</v>
+        <v>20.71300000000001</v>
       </c>
       <c r="F88">
-        <v>120.314</v>
+        <v>121.713</v>
       </c>
       <c r="G88">
         <v>2.19</v>
@@ -8491,37 +8491,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M88">
-        <v>28.3700412</v>
+        <v>28.6999254</v>
       </c>
       <c r="N88">
-        <v>-19.40670786666667</v>
+        <v>-19.73659206666667</v>
       </c>
       <c r="O88">
-        <v>-4.463542809333334</v>
+        <v>-4.539416175333334</v>
       </c>
       <c r="P88">
-        <v>-14.94316505733333</v>
+        <v>-15.19717589133333</v>
       </c>
       <c r="Q88">
-        <v>-11.42316505733334</v>
+        <v>-11.67717589133333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4234165511430802</v>
+        <v>0.4524639781540865</v>
       </c>
       <c r="T88">
-        <v>5.841607949729045</v>
+        <v>6.29096240740051</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07266703111684825</v>
+        <v>0.0718317778856201</v>
       </c>
       <c r="W88">
-        <v>0.2186651140626472</v>
+        <v>0.2188620667745708</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3159436135515141</v>
+        <v>0.3123120777635657</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2492303152539078</v>
+        <v>0.2511303152539078</v>
       </c>
       <c r="C89">
-        <v>-82.36369998911422</v>
+        <v>-84.10654921533967</v>
       </c>
       <c r="D89">
-        <v>37.15930001088579</v>
+        <v>36.81545078466035</v>
       </c>
       <c r="E89">
-        <v>20.71300000000001</v>
+        <v>22.11200000000001</v>
       </c>
       <c r="F89">
-        <v>121.713</v>
+        <v>123.112</v>
       </c>
       <c r="G89">
         <v>2.19</v>
@@ -8573,37 +8573,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M89">
-        <v>28.6999254</v>
+        <v>29.0298096</v>
       </c>
       <c r="N89">
-        <v>-19.73659206666667</v>
+        <v>-20.06647626666667</v>
       </c>
       <c r="O89">
-        <v>-4.539416175333334</v>
+        <v>-4.615289541333334</v>
       </c>
       <c r="P89">
-        <v>-15.19717589133333</v>
+        <v>-15.45118672533333</v>
       </c>
       <c r="Q89">
-        <v>-11.67717589133333</v>
+        <v>-11.93118672533334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4524639781540865</v>
+        <v>0.4863526430002604</v>
       </c>
       <c r="T89">
-        <v>6.29096240740051</v>
+        <v>6.815209274683887</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0718317778856201</v>
+        <v>0.07101550768237443</v>
       </c>
       <c r="W89">
-        <v>0.2188620667745708</v>
+        <v>0.2190545432884961</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3123120777635657</v>
+        <v>0.3087630768798888</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2511303152539078</v>
+        <v>0.2530303152539078</v>
       </c>
       <c r="C90">
-        <v>-84.10654921533967</v>
+        <v>-85.84309324891964</v>
       </c>
       <c r="D90">
-        <v>36.81545078466035</v>
+        <v>36.47790675108037</v>
       </c>
       <c r="E90">
-        <v>22.11200000000001</v>
+        <v>23.51100000000001</v>
       </c>
       <c r="F90">
-        <v>123.112</v>
+        <v>124.511</v>
       </c>
       <c r="G90">
         <v>2.19</v>
@@ -8655,37 +8655,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M90">
-        <v>29.0298096</v>
+        <v>29.3596938</v>
       </c>
       <c r="N90">
-        <v>-20.06647626666667</v>
+        <v>-20.39636046666667</v>
       </c>
       <c r="O90">
-        <v>-4.615289541333334</v>
+        <v>-4.691162907333334</v>
       </c>
       <c r="P90">
-        <v>-15.45118672533333</v>
+        <v>-15.70519755933333</v>
       </c>
       <c r="Q90">
-        <v>-11.93118672533334</v>
+        <v>-12.18519755933333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4863526430002604</v>
+        <v>0.5264028832730113</v>
       </c>
       <c r="T90">
-        <v>6.815209274683887</v>
+        <v>7.434773754200604</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07101550768237443</v>
+        <v>0.07021758062976348</v>
       </c>
       <c r="W90">
-        <v>0.2190545432884961</v>
+        <v>0.2192426944875018</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3087630768798888</v>
+        <v>0.3052938288250586</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2530303152539078</v>
+        <v>0.2549303152539079</v>
       </c>
       <c r="C91">
-        <v>-85.84309324891964</v>
+        <v>-87.57350394250037</v>
       </c>
       <c r="D91">
-        <v>36.47790675108037</v>
+        <v>36.14649605749965</v>
       </c>
       <c r="E91">
-        <v>23.51100000000001</v>
+        <v>24.91000000000001</v>
       </c>
       <c r="F91">
-        <v>124.511</v>
+        <v>125.91</v>
       </c>
       <c r="G91">
         <v>2.19</v>
@@ -8737,37 +8737,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M91">
-        <v>29.3596938</v>
+        <v>29.689578</v>
       </c>
       <c r="N91">
-        <v>-20.39636046666667</v>
+        <v>-20.72624466666667</v>
       </c>
       <c r="O91">
-        <v>-4.691162907333334</v>
+        <v>-4.767036273333335</v>
       </c>
       <c r="P91">
-        <v>-15.70519755933333</v>
+        <v>-15.95920839333333</v>
       </c>
       <c r="Q91">
-        <v>-12.18519755933333</v>
+        <v>-12.43920839333333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5264028832730113</v>
+        <v>0.5744631716003125</v>
       </c>
       <c r="T91">
-        <v>7.434773754200604</v>
+        <v>8.178251129620666</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07021758062976348</v>
+        <v>0.06943738528943276</v>
       </c>
       <c r="W91">
-        <v>0.2192426944875018</v>
+        <v>0.2194266645487518</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3052938288250586</v>
+        <v>0.3019016751714468</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2549303152539079</v>
+        <v>0.2568303152539078</v>
       </c>
       <c r="C92">
-        <v>-87.57350394250037</v>
+        <v>-89.2979469596641</v>
       </c>
       <c r="D92">
-        <v>36.14649605749965</v>
+        <v>35.8210530403359</v>
       </c>
       <c r="E92">
-        <v>24.91000000000001</v>
+        <v>26.30900000000001</v>
       </c>
       <c r="F92">
-        <v>125.91</v>
+        <v>127.309</v>
       </c>
       <c r="G92">
         <v>2.19</v>
@@ -8819,37 +8819,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M92">
-        <v>29.689578</v>
+        <v>30.0194622</v>
       </c>
       <c r="N92">
-        <v>-20.72624466666667</v>
+        <v>-21.05612886666667</v>
       </c>
       <c r="O92">
-        <v>-4.767036273333335</v>
+        <v>-4.842909639333334</v>
       </c>
       <c r="P92">
-        <v>-15.95920839333333</v>
+        <v>-16.21321922733333</v>
       </c>
       <c r="Q92">
-        <v>-12.43920839333333</v>
+        <v>-12.69321922733333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5744631716003125</v>
+        <v>0.6332035240003472</v>
       </c>
       <c r="T92">
-        <v>8.178251129620666</v>
+        <v>9.086945699578518</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06943738528943276</v>
+        <v>0.068674337099439</v>
       </c>
       <c r="W92">
-        <v>0.2194266645487518</v>
+        <v>0.2196065913119523</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3019016751714468</v>
+        <v>0.2985840743453869</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2568303152539078</v>
+        <v>0.2587303152539078</v>
       </c>
       <c r="C93">
-        <v>-89.2979469596641</v>
+        <v>-91.01658205105764</v>
       </c>
       <c r="D93">
-        <v>35.8210530403359</v>
+        <v>35.50141794894237</v>
       </c>
       <c r="E93">
-        <v>26.30900000000001</v>
+        <v>27.708</v>
       </c>
       <c r="F93">
-        <v>127.309</v>
+        <v>128.708</v>
       </c>
       <c r="G93">
         <v>2.19</v>
@@ -8901,37 +8901,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M93">
-        <v>30.0194622</v>
+        <v>30.3493464</v>
       </c>
       <c r="N93">
-        <v>-21.05612886666667</v>
+        <v>-21.38601306666667</v>
       </c>
       <c r="O93">
-        <v>-4.842909639333334</v>
+        <v>-4.918783005333333</v>
       </c>
       <c r="P93">
-        <v>-16.21321922733333</v>
+        <v>-16.46723006133333</v>
       </c>
       <c r="Q93">
-        <v>-12.69321922733333</v>
+        <v>-12.94723006133333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6332035240003472</v>
+        <v>0.7066289645003908</v>
       </c>
       <c r="T93">
-        <v>9.086945699578518</v>
+        <v>10.22281391202583</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.068674337099439</v>
+        <v>0.06792787691357553</v>
       </c>
       <c r="W93">
-        <v>0.2196065913119523</v>
+        <v>0.2197826066237789</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2985840743453869</v>
+        <v>0.2953385952764154</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2587303152539078</v>
+        <v>0.2606303152539078</v>
       </c>
       <c r="C94">
-        <v>-91.01658205105764</v>
+        <v>-92.72956331586781</v>
       </c>
       <c r="D94">
-        <v>35.50141794894237</v>
+        <v>35.18743668413219</v>
       </c>
       <c r="E94">
-        <v>27.708</v>
+        <v>29.107</v>
       </c>
       <c r="F94">
-        <v>128.708</v>
+        <v>130.107</v>
       </c>
       <c r="G94">
         <v>2.19</v>
@@ -8983,37 +8983,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M94">
-        <v>30.3493464</v>
+        <v>30.6792306</v>
       </c>
       <c r="N94">
-        <v>-21.38601306666667</v>
+        <v>-21.71589726666667</v>
       </c>
       <c r="O94">
-        <v>-4.918783005333333</v>
+        <v>-4.994656371333333</v>
       </c>
       <c r="P94">
-        <v>-16.46723006133333</v>
+        <v>-16.72124089533333</v>
       </c>
       <c r="Q94">
-        <v>-12.94723006133333</v>
+        <v>-13.20124089533333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7066289645003908</v>
+        <v>0.8010331022861611</v>
       </c>
       <c r="T94">
-        <v>10.22281391202583</v>
+        <v>11.6832158994581</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06792787691357553</v>
+        <v>0.06719746963493495</v>
       </c>
       <c r="W94">
-        <v>0.2197826066237789</v>
+        <v>0.2199548366600824</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2953385952764154</v>
+        <v>0.2921629114562388</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2606303152539078</v>
+        <v>0.2625303152539078</v>
       </c>
       <c r="C95">
-        <v>-92.72956331586781</v>
+        <v>-94.43703944954356</v>
       </c>
       <c r="D95">
-        <v>35.18743668413219</v>
+        <v>34.87896055045645</v>
       </c>
       <c r="E95">
-        <v>29.107</v>
+        <v>30.506</v>
       </c>
       <c r="F95">
-        <v>130.107</v>
+        <v>131.506</v>
       </c>
       <c r="G95">
         <v>2.19</v>
@@ -9065,37 +9065,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M95">
-        <v>30.6792306</v>
+        <v>31.0091148</v>
       </c>
       <c r="N95">
-        <v>-21.71589726666667</v>
+        <v>-22.04578146666667</v>
       </c>
       <c r="O95">
-        <v>-4.994656371333333</v>
+        <v>-5.070529737333334</v>
       </c>
       <c r="P95">
-        <v>-16.72124089533333</v>
+        <v>-16.97525172933333</v>
       </c>
       <c r="Q95">
-        <v>-13.20124089533333</v>
+        <v>-13.45525172933333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8010331022861611</v>
+        <v>0.9269052860005215</v>
       </c>
       <c r="T95">
-        <v>11.6832158994581</v>
+        <v>13.63041854936779</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06719746963493495</v>
+        <v>0.06648260293669096</v>
       </c>
       <c r="W95">
-        <v>0.2199548366600824</v>
+        <v>0.2201234022275283</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2921629114562388</v>
+        <v>0.2890547953769171</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2625303152539078</v>
+        <v>0.2644303152539078</v>
       </c>
       <c r="C96">
-        <v>-94.43703944954356</v>
+        <v>-96.13915397860099</v>
       </c>
       <c r="D96">
-        <v>34.87896055045645</v>
+        <v>34.57584602139902</v>
       </c>
       <c r="E96">
-        <v>30.506</v>
+        <v>31.905</v>
       </c>
       <c r="F96">
-        <v>131.506</v>
+        <v>132.905</v>
       </c>
       <c r="G96">
         <v>2.19</v>
@@ -9147,37 +9147,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M96">
-        <v>31.0091148</v>
+        <v>31.338999</v>
       </c>
       <c r="N96">
-        <v>-22.04578146666667</v>
+        <v>-22.37566566666667</v>
       </c>
       <c r="O96">
-        <v>-5.070529737333334</v>
+        <v>-5.146403103333333</v>
       </c>
       <c r="P96">
-        <v>-16.97525172933333</v>
+        <v>-17.22926256333333</v>
       </c>
       <c r="Q96">
-        <v>-13.45525172933333</v>
+        <v>-13.70926256333333</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9269052860005215</v>
+        <v>1.103126343200626</v>
       </c>
       <c r="T96">
-        <v>13.63041854936779</v>
+        <v>16.35650225924135</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06648260293669096</v>
+        <v>0.06578278606367316</v>
       </c>
       <c r="W96">
-        <v>0.2201234022275283</v>
+        <v>0.2202884190461859</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2890547953769171</v>
+        <v>0.2860121133203181</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2644303152539078</v>
+        <v>0.2663303152539079</v>
       </c>
       <c r="C97">
-        <v>-96.13915397860099</v>
+        <v>-97.8360454832906</v>
       </c>
       <c r="D97">
-        <v>34.57584602139902</v>
+        <v>34.27795451670939</v>
       </c>
       <c r="E97">
-        <v>31.905</v>
+        <v>33.304</v>
       </c>
       <c r="F97">
-        <v>132.905</v>
+        <v>134.304</v>
       </c>
       <c r="G97">
         <v>2.19</v>
@@ -9229,37 +9229,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M97">
-        <v>31.338999</v>
+        <v>31.6688832</v>
       </c>
       <c r="N97">
-        <v>-22.37566566666667</v>
+        <v>-22.70554986666667</v>
       </c>
       <c r="O97">
-        <v>-5.146403103333333</v>
+        <v>-5.222276469333334</v>
       </c>
       <c r="P97">
-        <v>-17.22926256333333</v>
+        <v>-17.48327339733333</v>
       </c>
       <c r="Q97">
-        <v>-13.70926256333333</v>
+        <v>-13.96327339733334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.103126343200626</v>
+        <v>1.367457929000784</v>
       </c>
       <c r="T97">
-        <v>16.35650225924135</v>
+        <v>20.4456278240517</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06578278606367316</v>
+        <v>0.06509754870884323</v>
       </c>
       <c r="W97">
-        <v>0.2202884190461859</v>
+        <v>0.2204499980144548</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2860121133203181</v>
+        <v>0.2830328204732314</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2663303152539078</v>
+        <v>0.2682303152539078</v>
       </c>
       <c r="C98">
-        <v>-97.8360454832906</v>
+        <v>-99.52784780885221</v>
       </c>
       <c r="D98">
-        <v>34.27795451670941</v>
+        <v>33.98515219114779</v>
       </c>
       <c r="E98">
-        <v>33.304</v>
+        <v>34.703</v>
       </c>
       <c r="F98">
-        <v>134.304</v>
+        <v>135.703</v>
       </c>
       <c r="G98">
         <v>2.19</v>
@@ -9311,37 +9311,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M98">
-        <v>31.6688832</v>
+        <v>31.9987674</v>
       </c>
       <c r="N98">
-        <v>-22.70554986666667</v>
+        <v>-23.03543406666667</v>
       </c>
       <c r="O98">
-        <v>-5.222276469333334</v>
+        <v>-5.298149835333334</v>
       </c>
       <c r="P98">
-        <v>-17.48327339733333</v>
+        <v>-17.73728423133333</v>
       </c>
       <c r="Q98">
-        <v>-13.96327339733334</v>
+        <v>-14.21728423133333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.36745792900078</v>
+        <v>1.80801057200104</v>
       </c>
       <c r="T98">
-        <v>20.44562782405164</v>
+        <v>27.26083709873553</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06509754870884323</v>
+        <v>0.06442643995926753</v>
       </c>
       <c r="W98">
-        <v>0.2204499980144548</v>
+        <v>0.2206082454576047</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2830328204732314</v>
+        <v>0.2801149563446413</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2682303152539078</v>
+        <v>0.2701303152539078</v>
       </c>
       <c r="C99">
-        <v>-99.52784780885221</v>
+        <v>-101.2146902660346</v>
       </c>
       <c r="D99">
-        <v>33.98515219114779</v>
+        <v>33.69730973396541</v>
       </c>
       <c r="E99">
-        <v>34.703</v>
+        <v>36.102</v>
       </c>
       <c r="F99">
-        <v>135.703</v>
+        <v>137.102</v>
       </c>
       <c r="G99">
         <v>2.19</v>
@@ -9393,37 +9393,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M99">
-        <v>31.9987674</v>
+        <v>32.3286516</v>
       </c>
       <c r="N99">
-        <v>-23.03543406666667</v>
+        <v>-23.36531826666667</v>
       </c>
       <c r="O99">
-        <v>-5.298149835333334</v>
+        <v>-5.374023201333333</v>
       </c>
       <c r="P99">
-        <v>-17.73728423133333</v>
+        <v>-17.99129506533333</v>
       </c>
       <c r="Q99">
-        <v>-14.21728423133333</v>
+        <v>-14.47129506533333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.80801057200104</v>
+        <v>2.689115858001559</v>
       </c>
       <c r="T99">
-        <v>27.26083709873553</v>
+        <v>40.89125564810328</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06442643995926753</v>
+        <v>0.06376902730662194</v>
       </c>
       <c r="W99">
-        <v>0.2206082454576047</v>
+        <v>0.2207632633610986</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2801149563446413</v>
+        <v>0.2772566404635737</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2701303152539078</v>
+        <v>0.2720303152539078</v>
       </c>
       <c r="C100">
-        <v>-101.2146902660346</v>
+        <v>-102.8966978215104</v>
       </c>
       <c r="D100">
-        <v>33.69730973396541</v>
+        <v>33.41430217848959</v>
       </c>
       <c r="E100">
-        <v>36.102</v>
+        <v>37.501</v>
       </c>
       <c r="F100">
-        <v>137.102</v>
+        <v>138.501</v>
       </c>
       <c r="G100">
         <v>2.19</v>
@@ -9475,37 +9475,37 @@
         <v>8.963333333333335</v>
       </c>
       <c r="M100">
-        <v>32.3286516</v>
+        <v>32.6585358</v>
       </c>
       <c r="N100">
-        <v>-23.36531826666667</v>
+        <v>-23.69520246666667</v>
       </c>
       <c r="O100">
-        <v>-5.374023201333333</v>
+        <v>-5.449896567333334</v>
       </c>
       <c r="P100">
-        <v>-17.99129506533333</v>
+        <v>-18.24530589933334</v>
       </c>
       <c r="Q100">
-        <v>-14.47129506533333</v>
+        <v>-14.72530589933334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.689115858001559</v>
+        <v>5.332431716003119</v>
       </c>
       <c r="T100">
-        <v>40.89125564810328</v>
+        <v>81.78251129620656</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06376902730662194</v>
+        <v>0.06312489571766616</v>
       </c>
       <c r="W100">
-        <v>0.2207632633610986</v>
+        <v>0.2209151495897743</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2772566404635737</v>
+        <v>0.2744560683376789</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2720303152539078</v>
-      </c>
-      <c r="C101">
-        <v>-102.8966978215104</v>
-      </c>
-      <c r="D101">
-        <v>33.41430217848959</v>
-      </c>
-      <c r="E101">
-        <v>37.501</v>
-      </c>
-      <c r="F101">
-        <v>138.501</v>
-      </c>
-      <c r="G101">
-        <v>2.19</v>
-      </c>
-      <c r="H101">
-        <v>38.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.48333333333333</v>
-      </c>
-      <c r="K101">
-        <v>3.52</v>
-      </c>
-      <c r="L101">
-        <v>8.963333333333335</v>
-      </c>
-      <c r="M101">
-        <v>32.6585358</v>
-      </c>
-      <c r="N101">
-        <v>-23.69520246666667</v>
-      </c>
-      <c r="O101">
-        <v>-5.449896567333334</v>
-      </c>
-      <c r="P101">
-        <v>-18.24530589933334</v>
-      </c>
-      <c r="Q101">
-        <v>-14.72530589933334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.332431716003119</v>
-      </c>
-      <c r="T101">
-        <v>81.78251129620656</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06312489571766616</v>
-      </c>
-      <c r="W101">
-        <v>0.2209151495897743</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2744560683376789</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
